--- a/Financial Analysis/DAI.xlsx
+++ b/Financial Analysis/DAI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9856D22-029D-45B0-A996-AE124AEAB52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DBB970-4898-4913-8523-FC5936700EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{C8793F2E-CDC7-4BB8-B5F3-F499391B70FF}"/>
   </bookViews>
@@ -320,7 +320,7 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Slightly undervalued</t>
   </si>
 </sst>
 </file>
@@ -462,14 +462,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
@@ -486,7 +486,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19210020" y="0"/>
+          <a:off x="20436840" y="0"/>
           <a:ext cx="0" cy="7414260"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -888,17 +888,17 @@
         <v>11</v>
       </c>
       <c r="D3" s="4">
-        <v>53.31</v>
+        <v>53.35</v>
       </c>
       <c r="E3" s="5">
-        <v>45771</v>
+        <v>45899</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45771</v>
+        <v>45904</v>
       </c>
       <c r="G3" s="5">
-        <v>45777</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -906,10 +906,11 @@
         <v>12</v>
       </c>
       <c r="D4" s="6">
-        <v>1013.6</v>
+        <f>962.9</f>
+        <v>962.9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -919,7 +920,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>54035.016000000003</v>
+        <v>51370.715000000004</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -929,11 +930,11 @@
         <v>14</v>
       </c>
       <c r="D6" s="6">
-        <f>14511+7086</f>
-        <v>21597</v>
+        <f>9962+11752+618</f>
+        <v>22332</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -942,11 +943,11 @@
         <v>15</v>
       </c>
       <c r="D7" s="6">
-        <f>39311+73487</f>
-        <v>112798</v>
+        <f>37909+68407</f>
+        <v>106316</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -956,7 +957,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>-91201</v>
+        <v>-83984</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -967,7 +968,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>145236.016</v>
+        <v>135354.715</v>
       </c>
     </row>
   </sheetData>
@@ -1239,10 +1240,20 @@
         <f>AP3-AC3-AB3-AA3</f>
         <v>38450</v>
       </c>
-      <c r="AE3" s="8"/>
-      <c r="AF3" s="8"/>
-      <c r="AG3" s="8"/>
-      <c r="AH3" s="8"/>
+      <c r="AE3" s="8">
+        <v>33224</v>
+      </c>
+      <c r="AF3" s="8">
+        <v>33153</v>
+      </c>
+      <c r="AG3" s="8">
+        <f>AC3*0.94</f>
+        <v>32456.32</v>
+      </c>
+      <c r="AH3" s="8">
+        <f>AD3*0.97</f>
+        <v>37296.5</v>
+      </c>
       <c r="AJ3" s="8">
         <f>SUM(C3:F3)</f>
         <v>167362</v>
@@ -1267,48 +1278,48 @@
         <v>145594</v>
       </c>
       <c r="AQ3" s="8">
-        <f>AP3*0.98</f>
-        <v>142682.12</v>
+        <f>SUM(AE3:AH3)</f>
+        <v>136129.82</v>
       </c>
       <c r="AR3" s="8">
-        <f>AQ3*1.01</f>
-        <v>144108.9412</v>
+        <f>AQ3*1.03</f>
+        <v>140213.71460000001</v>
       </c>
       <c r="AS3" s="8">
-        <f t="shared" ref="AS3:BA3" si="0">AR3*1.01</f>
-        <v>145550.030612</v>
+        <f>AR3*1.02</f>
+        <v>143017.98889200002</v>
       </c>
       <c r="AT3" s="8">
-        <f t="shared" si="0"/>
-        <v>147005.53091812</v>
+        <f t="shared" ref="AT3:BA3" si="0">AS3*1.01</f>
+        <v>144448.16878092004</v>
       </c>
       <c r="AU3" s="8">
         <f t="shared" si="0"/>
-        <v>148475.58622730119</v>
+        <v>145892.65046872923</v>
       </c>
       <c r="AV3" s="8">
         <f t="shared" si="0"/>
-        <v>149960.3420895742</v>
+        <v>147351.57697341652</v>
       </c>
       <c r="AW3" s="8">
         <f t="shared" si="0"/>
-        <v>151459.94551046996</v>
+        <v>148825.09274315069</v>
       </c>
       <c r="AX3" s="8">
         <f t="shared" si="0"/>
-        <v>152974.54496557466</v>
+        <v>150313.3436705822</v>
       </c>
       <c r="AY3" s="8">
         <f t="shared" si="0"/>
-        <v>154504.29041523041</v>
+        <v>151816.47710728802</v>
       </c>
       <c r="AZ3" s="8">
         <f t="shared" si="0"/>
-        <v>156049.33331938271</v>
+        <v>153334.64187836091</v>
       </c>
       <c r="BA3" s="8">
         <f t="shared" si="0"/>
-        <v>157609.82665257654</v>
+        <v>154867.98829714453</v>
       </c>
     </row>
     <row r="4" spans="2:53" x14ac:dyDescent="0.3">
@@ -1406,10 +1417,20 @@
         <f>AP4-AC4-AB4-AA4</f>
         <v>31016</v>
       </c>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="6"/>
-      <c r="AH4" s="6"/>
+      <c r="AE4" s="6">
+        <v>26660</v>
+      </c>
+      <c r="AF4" s="6">
+        <v>27711</v>
+      </c>
+      <c r="AG4" s="6">
+        <f t="shared" ref="AG4:AH4" si="1">AG3-AG5</f>
+        <v>25965.056</v>
+      </c>
+      <c r="AH4" s="6">
+        <f t="shared" si="1"/>
+        <v>29837.200000000001</v>
+      </c>
       <c r="AJ4" s="6">
         <f>SUM(C4:F4)</f>
         <v>134295</v>
@@ -1434,48 +1455,48 @@
         <v>117018</v>
       </c>
       <c r="AQ4" s="6">
-        <f t="shared" ref="AQ4:AV4" si="1">AQ3-AQ5</f>
-        <v>112718.87479999999</v>
+        <f>SUM(AE4:AH4)</f>
+        <v>110173.25599999999</v>
       </c>
       <c r="AR4" s="6">
-        <f t="shared" si="1"/>
-        <v>113846.06354800001</v>
+        <f t="shared" ref="AR4:AV4" si="2">AR3-AR5</f>
+        <v>110768.83453400001</v>
       </c>
       <c r="AS4" s="6">
-        <f t="shared" si="1"/>
-        <v>114984.52418348001</v>
+        <f t="shared" si="2"/>
+        <v>112984.21122468002</v>
       </c>
       <c r="AT4" s="6">
-        <f t="shared" si="1"/>
-        <v>116134.3694253148</v>
+        <f t="shared" si="2"/>
+        <v>112669.57164911763</v>
       </c>
       <c r="AU4" s="6">
-        <f t="shared" si="1"/>
-        <v>117295.71311956794</v>
+        <f t="shared" si="2"/>
+        <v>113796.2673656088</v>
       </c>
       <c r="AV4" s="6">
-        <f t="shared" si="1"/>
-        <v>118468.67025076362</v>
+        <f t="shared" si="2"/>
+        <v>114934.23003926489</v>
       </c>
       <c r="AW4" s="6">
-        <f t="shared" ref="AW4:BA4" si="2">AW3-AW5</f>
-        <v>119653.35695327127</v>
+        <f t="shared" ref="AW4:BA4" si="3">AW3-AW5</f>
+        <v>116083.57233965753</v>
       </c>
       <c r="AX4" s="6">
-        <f t="shared" si="2"/>
-        <v>120849.89052280398</v>
+        <f t="shared" si="3"/>
+        <v>117244.40806305411</v>
       </c>
       <c r="AY4" s="6">
-        <f t="shared" si="2"/>
-        <v>122058.38942803202</v>
+        <f t="shared" si="3"/>
+        <v>118416.85214368466</v>
       </c>
       <c r="AZ4" s="6">
-        <f t="shared" si="2"/>
-        <v>123278.97332231235</v>
+        <f t="shared" si="3"/>
+        <v>119601.02066512151</v>
       </c>
       <c r="BA4" s="6">
-        <f t="shared" si="2"/>
-        <v>124511.76305553547</v>
+        <f t="shared" si="3"/>
+        <v>120797.03087177273</v>
       </c>
     </row>
     <row r="5" spans="2:53" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1483,121 +1504,133 @@
         <v>18</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:N5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:N5" si="4">C3-C4</f>
         <v>8625</v>
       </c>
       <c r="D5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8250</v>
       </c>
       <c r="E5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7964</v>
       </c>
       <c r="F5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8228</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7571</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5546</v>
       </c>
       <c r="I5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8674</v>
       </c>
       <c r="J5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7374</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5711</v>
       </c>
       <c r="L5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2695</v>
       </c>
       <c r="M5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7577</v>
       </c>
       <c r="N5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9605</v>
       </c>
       <c r="O5" s="8">
-        <f t="shared" ref="O5:P5" si="4">O3-O4</f>
+        <f t="shared" ref="O5:P5" si="5">O3-O4</f>
         <v>7386</v>
       </c>
       <c r="P5" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7902</v>
       </c>
       <c r="Q5" s="8">
-        <f t="shared" ref="Q5:R5" si="5">Q3-Q4</f>
+        <f t="shared" ref="Q5:R5" si="6">Q3-Q4</f>
         <v>6714</v>
       </c>
       <c r="R5" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8673</v>
       </c>
       <c r="S5" s="8">
-        <f t="shared" ref="S5:T5" si="6">S3-S4</f>
+        <f t="shared" ref="S5:T5" si="7">S3-S4</f>
         <v>7964</v>
       </c>
       <c r="T5" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8502</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" ref="U5:V5" si="7">U3-U4</f>
+        <f t="shared" ref="U5:V5" si="8">U3-U4</f>
         <v>8782</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8772</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" ref="W5:X5" si="8">W3-W4</f>
+        <f t="shared" ref="W5:X5" si="9">W3-W4</f>
         <v>9450</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8957</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" ref="Y5:AC5" si="9">Y3-Y4</f>
+        <f t="shared" ref="Y5:AC5" si="10">Y3-Y4</f>
         <v>8034</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" ref="Z5" si="10">Z3-Z4</f>
+        <f t="shared" ref="Z5" si="11">Z3-Z4</f>
         <v>7938</v>
       </c>
       <c r="AA5" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7106</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7824</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6212</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" ref="AD5" si="11">AD3*0.2</f>
+        <f t="shared" ref="AD5" si="12">AD3*0.2</f>
         <v>7690</v>
       </c>
-      <c r="AE5" s="8"/>
-      <c r="AF5" s="8"/>
-      <c r="AG5" s="8"/>
-      <c r="AH5" s="8"/>
+      <c r="AE5" s="8">
+        <f t="shared" ref="AE5:AF5" si="13">AE3-AE4</f>
+        <v>6564</v>
+      </c>
+      <c r="AF5" s="8">
+        <f t="shared" si="13"/>
+        <v>5442</v>
+      </c>
+      <c r="AG5" s="8">
+        <f t="shared" ref="AG5:AH5" si="14">AG3*0.2</f>
+        <v>6491.2640000000001</v>
+      </c>
+      <c r="AH5" s="8">
+        <f t="shared" si="14"/>
+        <v>7459.3</v>
+      </c>
       <c r="AJ5" s="8">
         <f>AJ3-AJ4</f>
         <v>33067</v>
@@ -1611,64 +1644,64 @@
         <v>25588</v>
       </c>
       <c r="AM5" s="8">
-        <f t="shared" ref="AM5" si="12">AM3-AM4</f>
+        <f t="shared" ref="AM5" si="15">AM3-AM4</f>
         <v>30675</v>
       </c>
       <c r="AN5" s="8">
-        <f t="shared" ref="AN5:AO5" si="13">AN3-AN4</f>
+        <f t="shared" ref="AN5:AO5" si="16">AN3-AN4</f>
         <v>34020</v>
       </c>
       <c r="AO5" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>34379</v>
       </c>
       <c r="AP5" s="8">
-        <f t="shared" ref="AP5" si="14">AP3-AP4</f>
+        <f t="shared" ref="AP5:AQ5" si="17">AP3-AP4</f>
         <v>28576</v>
       </c>
       <c r="AQ5" s="8">
-        <f>AQ3*0.21</f>
-        <v>29963.245199999998</v>
+        <f t="shared" si="17"/>
+        <v>25956.564000000013</v>
       </c>
       <c r="AR5" s="8">
-        <f t="shared" ref="AR5:BA5" si="15">AR3*0.21</f>
-        <v>30262.877651999999</v>
+        <f t="shared" ref="AR5:AS5" si="18">AR3*0.21</f>
+        <v>29444.880066000002</v>
       </c>
       <c r="AS5" s="8">
-        <f t="shared" si="15"/>
-        <v>30565.506428519999</v>
+        <f t="shared" si="18"/>
+        <v>30033.777667320002</v>
       </c>
       <c r="AT5" s="8">
-        <f t="shared" si="15"/>
-        <v>30871.1614928052</v>
+        <f>AT3*0.22</f>
+        <v>31778.597131802409</v>
       </c>
       <c r="AU5" s="8">
-        <f t="shared" si="15"/>
-        <v>31179.873107733249</v>
+        <f t="shared" ref="AU5:BA5" si="19">AU3*0.22</f>
+        <v>32096.383103120432</v>
       </c>
       <c r="AV5" s="8">
-        <f t="shared" si="15"/>
-        <v>31491.67183881058</v>
+        <f t="shared" si="19"/>
+        <v>32417.346934151636</v>
       </c>
       <c r="AW5" s="8">
-        <f t="shared" si="15"/>
-        <v>31806.588557198691</v>
+        <f t="shared" si="19"/>
+        <v>32741.520403493152</v>
       </c>
       <c r="AX5" s="8">
-        <f t="shared" si="15"/>
-        <v>32124.654442770679</v>
+        <f t="shared" si="19"/>
+        <v>33068.935607528081</v>
       </c>
       <c r="AY5" s="8">
-        <f t="shared" si="15"/>
-        <v>32445.900987198384</v>
+        <f t="shared" si="19"/>
+        <v>33399.624963603368</v>
       </c>
       <c r="AZ5" s="8">
-        <f t="shared" si="15"/>
-        <v>32770.359997070365</v>
+        <f t="shared" si="19"/>
+        <v>33733.621213239399</v>
       </c>
       <c r="BA5" s="8">
-        <f t="shared" si="15"/>
-        <v>33098.063597041073</v>
+        <f t="shared" si="19"/>
+        <v>34070.957425371795</v>
       </c>
     </row>
     <row r="6" spans="2:53" x14ac:dyDescent="0.3">
@@ -1730,7 +1763,7 @@
         <v>2199</v>
       </c>
       <c r="R6" s="6">
-        <f t="shared" ref="R6:R12" si="16">AM6-Q6-P6-O6</f>
+        <f t="shared" ref="R6:R12" si="20">AM6-Q6-P6-O6</f>
         <v>2535</v>
       </c>
       <c r="S6" s="6">
@@ -1743,7 +1776,7 @@
         <v>2456</v>
       </c>
       <c r="V6" s="6">
-        <f t="shared" ref="V6:V12" si="17">AN6-U6-T6-S6</f>
+        <f t="shared" ref="V6:V12" si="21">AN6-U6-T6-S6</f>
         <v>2395</v>
       </c>
       <c r="W6" s="6">
@@ -1756,7 +1789,7 @@
         <v>2368</v>
       </c>
       <c r="Z6" s="6">
-        <f t="shared" ref="Z6:Z12" si="18">AO6-Y6-X6-W6</f>
+        <f t="shared" ref="Z6:Z12" si="22">AO6-Y6-X6-W6</f>
         <v>2484</v>
       </c>
       <c r="AA6" s="6">
@@ -1769,13 +1802,23 @@
         <v>2143</v>
       </c>
       <c r="AD6" s="6">
-        <f t="shared" ref="AD6:AD12" si="19">AP6-AC6-AB6-AA6</f>
+        <f t="shared" ref="AD6:AD12" si="23">AP6-AC6-AB6-AA6</f>
         <v>3064</v>
       </c>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
+      <c r="AE6" s="6">
+        <v>2400</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>2450</v>
+      </c>
+      <c r="AG6" s="6">
+        <f>AG3*0.07</f>
+        <v>2271.9424000000004</v>
+      </c>
+      <c r="AH6" s="6">
+        <f t="shared" ref="AH6" si="24">AH3*0.07</f>
+        <v>2610.7550000000001</v>
+      </c>
       <c r="AJ6" s="6">
         <f>SUM(C6:F6)</f>
         <v>13067</v>
@@ -1801,48 +1844,48 @@
         <v>9993</v>
       </c>
       <c r="AQ6" s="6">
-        <f>AQ3*0.065</f>
-        <v>9274.3377999999993</v>
+        <f t="shared" ref="AQ6:AQ12" si="25">SUM(AE6:AH6)</f>
+        <v>9732.6974000000009</v>
       </c>
       <c r="AR6" s="6">
-        <f t="shared" ref="AR6:AW6" si="20">AR3*0.065</f>
-        <v>9367.0811780000004</v>
+        <f t="shared" ref="AR6:AW6" si="26">AR3*0.065</f>
+        <v>9113.8914490000006</v>
       </c>
       <c r="AS6" s="6">
-        <f t="shared" si="20"/>
-        <v>9460.7519897800012</v>
+        <f t="shared" si="26"/>
+        <v>9296.1692779800014</v>
       </c>
       <c r="AT6" s="6">
-        <f t="shared" si="20"/>
-        <v>9555.3595096778008</v>
+        <f t="shared" si="26"/>
+        <v>9389.1309707598029</v>
       </c>
       <c r="AU6" s="6">
-        <f t="shared" si="20"/>
-        <v>9650.9131047745777</v>
+        <f t="shared" si="26"/>
+        <v>9483.0222804674013</v>
       </c>
       <c r="AV6" s="6">
-        <f t="shared" si="20"/>
-        <v>9747.4222358223233</v>
+        <f t="shared" si="26"/>
+        <v>9577.8525032720736</v>
       </c>
       <c r="AW6" s="6">
-        <f t="shared" si="20"/>
-        <v>9844.8964581805485</v>
+        <f t="shared" si="26"/>
+        <v>9673.6310283047951</v>
       </c>
       <c r="AX6" s="6">
-        <f t="shared" ref="AX6:BA6" si="21">AX3*0.065</f>
-        <v>9943.3454227623533</v>
+        <f t="shared" ref="AX6:BA6" si="27">AX3*0.065</f>
+        <v>9770.3673385878428</v>
       </c>
       <c r="AY6" s="6">
-        <f t="shared" si="21"/>
-        <v>10042.778876989976</v>
+        <f t="shared" si="27"/>
+        <v>9868.0710119737214</v>
       </c>
       <c r="AZ6" s="6">
-        <f t="shared" si="21"/>
-        <v>10143.206665759877</v>
+        <f t="shared" si="27"/>
+        <v>9966.7517220934587</v>
       </c>
       <c r="BA6" s="6">
-        <f t="shared" si="21"/>
-        <v>10244.638732417476</v>
+        <f t="shared" si="27"/>
+        <v>10066.419239314395</v>
       </c>
     </row>
     <row r="7" spans="2:53" x14ac:dyDescent="0.3">
@@ -1898,7 +1941,7 @@
         <v>707</v>
       </c>
       <c r="R7" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>771</v>
       </c>
       <c r="S7" s="6">
@@ -1911,7 +1954,7 @@
         <v>614</v>
       </c>
       <c r="V7" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>770</v>
       </c>
       <c r="W7" s="6">
@@ -1924,7 +1967,7 @@
         <v>606</v>
       </c>
       <c r="Z7" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>669</v>
       </c>
       <c r="AA7" s="6">
@@ -1937,15 +1980,25 @@
         <v>610</v>
       </c>
       <c r="AD7" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>584</v>
       </c>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="6"/>
+      <c r="AE7" s="6">
+        <v>660</v>
+      </c>
+      <c r="AF7" s="6">
+        <v>672</v>
+      </c>
+      <c r="AG7" s="6">
+        <f t="shared" ref="AG7" si="28">AC7*0.9</f>
+        <v>549</v>
+      </c>
+      <c r="AH7" s="6">
+        <f>AD7*1.03</f>
+        <v>601.52</v>
+      </c>
       <c r="AJ7" s="6">
-        <f t="shared" ref="AJ7" si="22">SUM(C7:F7)</f>
+        <f t="shared" ref="AJ7" si="29">SUM(C7:F7)</f>
         <v>4036</v>
       </c>
       <c r="AK7" s="6">
@@ -1968,48 +2021,48 @@
         <v>2529</v>
       </c>
       <c r="AQ7" s="6">
-        <f>AP7*1.04</f>
-        <v>2630.1600000000003</v>
+        <f t="shared" si="25"/>
+        <v>2482.52</v>
       </c>
       <c r="AR7" s="6">
         <f>AQ7*1.03</f>
-        <v>2709.0648000000006</v>
+        <v>2556.9956000000002</v>
       </c>
       <c r="AS7" s="6">
         <f>AR7*1.02</f>
-        <v>2763.2460960000008</v>
+        <v>2608.1355120000003</v>
       </c>
       <c r="AT7" s="6">
-        <f t="shared" ref="AT7:AW7" si="23">AS7*1.02</f>
-        <v>2818.511017920001</v>
+        <f t="shared" ref="AT7:AV7" si="30">AS7*1.02</f>
+        <v>2660.2982222400005</v>
       </c>
       <c r="AU7" s="6">
-        <f t="shared" si="23"/>
-        <v>2874.8812382784013</v>
+        <f t="shared" si="30"/>
+        <v>2713.5041866848005</v>
       </c>
       <c r="AV7" s="6">
-        <f t="shared" si="23"/>
-        <v>2932.3788630439694</v>
+        <f t="shared" si="30"/>
+        <v>2767.7742704184966</v>
       </c>
       <c r="AW7" s="6">
-        <f t="shared" si="23"/>
-        <v>2991.0264403048491</v>
+        <f>AV7*1.01</f>
+        <v>2795.4520131226814</v>
       </c>
       <c r="AX7" s="6">
-        <f t="shared" ref="AX7:BA7" si="24">AW7*1.02</f>
-        <v>3050.8469691109462</v>
+        <f t="shared" ref="AX7:BA7" si="31">AW7*1.01</f>
+        <v>2823.406533253908</v>
       </c>
       <c r="AY7" s="6">
-        <f t="shared" si="24"/>
-        <v>3111.8639084931651</v>
+        <f t="shared" si="31"/>
+        <v>2851.6405985864471</v>
       </c>
       <c r="AZ7" s="6">
-        <f t="shared" si="24"/>
-        <v>3174.1011866630283</v>
+        <f t="shared" si="31"/>
+        <v>2880.1570045723115</v>
       </c>
       <c r="BA7" s="6">
-        <f t="shared" si="24"/>
-        <v>3237.5832103962889</v>
+        <f t="shared" si="31"/>
+        <v>2908.9585746180346</v>
       </c>
     </row>
     <row r="8" spans="2:53" x14ac:dyDescent="0.3">
@@ -2066,7 +2119,7 @@
         <v>1351</v>
       </c>
       <c r="R8" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1116</v>
       </c>
       <c r="S8" s="6">
@@ -2079,7 +2132,7 @@
         <v>1525</v>
       </c>
       <c r="V8" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>1251</v>
       </c>
       <c r="W8" s="6">
@@ -2092,7 +2145,7 @@
         <v>1541</v>
       </c>
       <c r="Z8" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1362</v>
       </c>
       <c r="AA8" s="6">
@@ -2105,13 +2158,23 @@
         <v>1682</v>
       </c>
       <c r="AD8" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>969</v>
       </c>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="6"/>
+      <c r="AE8" s="6">
+        <v>1607</v>
+      </c>
+      <c r="AF8" s="6">
+        <v>1460</v>
+      </c>
+      <c r="AG8" s="6">
+        <f>AC8*1.03</f>
+        <v>1732.46</v>
+      </c>
+      <c r="AH8" s="6">
+        <f>AD8*1.5</f>
+        <v>1453.5</v>
+      </c>
       <c r="AJ8" s="6">
         <f>SUM(C8:F8)</f>
         <v>6581</v>
@@ -2136,48 +2199,48 @@
         <v>5580</v>
       </c>
       <c r="AQ8" s="6">
-        <f>AP8*1.04</f>
-        <v>5803.2</v>
+        <f t="shared" si="25"/>
+        <v>6252.96</v>
       </c>
       <c r="AR8" s="6">
         <f>AQ8*1.03</f>
-        <v>5977.2960000000003</v>
+        <v>6440.5488000000005</v>
       </c>
       <c r="AS8" s="6">
         <f>AR8*1.02</f>
-        <v>6096.8419200000008</v>
+        <v>6569.3597760000002</v>
       </c>
       <c r="AT8" s="6">
-        <f t="shared" ref="AT8:AT13" si="25">AS8*1.02</f>
-        <v>6218.7787584000007</v>
+        <f t="shared" ref="AT8" si="32">AS8*1.02</f>
+        <v>6700.7469715200004</v>
       </c>
       <c r="AU8" s="6">
-        <f t="shared" ref="AU8:AU13" si="26">AT8*1.02</f>
-        <v>6343.1543335680008</v>
+        <f t="shared" ref="AU8" si="33">AT8*1.02</f>
+        <v>6834.7619109504003</v>
       </c>
       <c r="AV8" s="6">
-        <f t="shared" ref="AV8:AW12" si="27">AU8*1.01</f>
-        <v>6406.5858769036804</v>
+        <f t="shared" ref="AV8:AW12" si="34">AU8*1.01</f>
+        <v>6903.1095300599045</v>
       </c>
       <c r="AW8" s="6">
-        <f t="shared" si="27"/>
-        <v>6470.6517356727172</v>
+        <f t="shared" si="34"/>
+        <v>6972.1406253605037</v>
       </c>
       <c r="AX8" s="6">
-        <f t="shared" ref="AX8:AX12" si="28">AW8*1.01</f>
-        <v>6535.3582530294443</v>
+        <f t="shared" ref="AX8:AX12" si="35">AW8*1.01</f>
+        <v>7041.8620316141087</v>
       </c>
       <c r="AY8" s="6">
-        <f t="shared" ref="AY8:AY12" si="29">AX8*1.01</f>
-        <v>6600.7118355597386</v>
+        <f t="shared" ref="AY8:AY12" si="36">AX8*1.01</f>
+        <v>7112.2806519302494</v>
       </c>
       <c r="AZ8" s="6">
-        <f t="shared" ref="AZ8:AZ12" si="30">AY8*1.01</f>
-        <v>6666.718953915336</v>
+        <f t="shared" ref="AZ8:AZ12" si="37">AY8*1.01</f>
+        <v>7183.4034584495521</v>
       </c>
       <c r="BA8" s="6">
-        <f t="shared" ref="BA8:BA12" si="31">AZ8*1.01</f>
-        <v>6733.3861434544897</v>
+        <f t="shared" ref="BA8:BA12" si="38">AZ8*1.01</f>
+        <v>7255.2374930340475</v>
       </c>
     </row>
     <row r="9" spans="2:53" x14ac:dyDescent="0.3">
@@ -2206,7 +2269,7 @@
         <v>-562</v>
       </c>
       <c r="R9" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-694</v>
       </c>
       <c r="S9" s="6">
@@ -2219,7 +2282,7 @@
         <v>-491</v>
       </c>
       <c r="V9" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-928</v>
       </c>
       <c r="W9" s="6">
@@ -2232,7 +2295,7 @@
         <v>-507</v>
       </c>
       <c r="Z9" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-694</v>
       </c>
       <c r="AA9" s="6">
@@ -2245,13 +2308,23 @@
         <v>-426</v>
       </c>
       <c r="AD9" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>-757</v>
       </c>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-      <c r="AG9" s="6"/>
-      <c r="AH9" s="6"/>
+      <c r="AE9" s="6">
+        <v>-338</v>
+      </c>
+      <c r="AF9" s="6">
+        <v>-383</v>
+      </c>
+      <c r="AG9" s="6">
+        <f t="shared" ref="AG9:AH12" si="39">AC9*1.01</f>
+        <v>-430.26</v>
+      </c>
+      <c r="AH9" s="6">
+        <f t="shared" si="39"/>
+        <v>-764.57</v>
+      </c>
       <c r="AJ9" s="6"/>
       <c r="AK9" s="6"/>
       <c r="AL9" s="6"/>
@@ -2268,48 +2341,48 @@
         <v>-2507</v>
       </c>
       <c r="AQ9" s="6">
-        <f>AP9*1.01</f>
-        <v>-2532.0700000000002</v>
+        <f t="shared" si="25"/>
+        <v>-1915.83</v>
       </c>
       <c r="AR9" s="6">
-        <f t="shared" ref="AR9:BA9" si="32">AQ9*1.01</f>
-        <v>-2557.3907000000004</v>
+        <f t="shared" ref="AR9:AU9" si="40">AQ9*1.01</f>
+        <v>-1934.9883</v>
       </c>
       <c r="AS9" s="6">
-        <f t="shared" si="32"/>
-        <v>-2582.9646070000003</v>
+        <f t="shared" si="40"/>
+        <v>-1954.3381830000001</v>
       </c>
       <c r="AT9" s="6">
-        <f t="shared" si="32"/>
-        <v>-2608.7942530700002</v>
+        <f t="shared" si="40"/>
+        <v>-1973.8815648300001</v>
       </c>
       <c r="AU9" s="6">
-        <f t="shared" si="32"/>
-        <v>-2634.8821956007</v>
+        <f t="shared" si="40"/>
+        <v>-1993.6203804783001</v>
       </c>
       <c r="AV9" s="6">
-        <f t="shared" si="27"/>
-        <v>-2661.2310175567072</v>
+        <f t="shared" si="34"/>
+        <v>-2013.5565842830831</v>
       </c>
       <c r="AW9" s="6">
-        <f t="shared" si="27"/>
-        <v>-2687.8433277322742</v>
+        <f t="shared" si="34"/>
+        <v>-2033.6921501259139</v>
       </c>
       <c r="AX9" s="6">
-        <f t="shared" si="28"/>
-        <v>-2714.7217610095972</v>
+        <f t="shared" si="35"/>
+        <v>-2054.0290716271729</v>
       </c>
       <c r="AY9" s="6">
-        <f t="shared" si="29"/>
-        <v>-2741.8689786196933</v>
+        <f t="shared" si="36"/>
+        <v>-2074.5693623434445</v>
       </c>
       <c r="AZ9" s="6">
-        <f t="shared" si="30"/>
-        <v>-2769.2876684058901</v>
+        <f t="shared" si="37"/>
+        <v>-2095.3150559668788</v>
       </c>
       <c r="BA9" s="6">
-        <f t="shared" si="31"/>
-        <v>-2796.9805450899489</v>
+        <f t="shared" si="38"/>
+        <v>-2116.2682065265476</v>
       </c>
     </row>
     <row r="10" spans="2:53" x14ac:dyDescent="0.3">
@@ -2338,7 +2411,7 @@
         <v>244</v>
       </c>
       <c r="R10" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>1152</v>
       </c>
       <c r="S10" s="6">
@@ -2351,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="V10" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>123</v>
       </c>
       <c r="W10" s="6">
@@ -2364,7 +2437,7 @@
         <v>53</v>
       </c>
       <c r="Z10" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>54</v>
       </c>
       <c r="AA10" s="6">
@@ -2377,13 +2450,23 @@
         <v>72</v>
       </c>
       <c r="AD10" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>185</v>
       </c>
-      <c r="AE10" s="6"/>
-      <c r="AF10" s="6"/>
-      <c r="AG10" s="6"/>
-      <c r="AH10" s="6"/>
+      <c r="AE10" s="6">
+        <v>315</v>
+      </c>
+      <c r="AF10" s="6">
+        <v>255</v>
+      </c>
+      <c r="AG10" s="6">
+        <f t="shared" si="39"/>
+        <v>72.72</v>
+      </c>
+      <c r="AH10" s="6">
+        <f t="shared" si="39"/>
+        <v>186.85</v>
+      </c>
       <c r="AJ10" s="6"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="6"/>
@@ -2400,48 +2483,48 @@
         <v>483</v>
       </c>
       <c r="AQ10" s="6">
-        <f t="shared" ref="AQ10:BA10" si="33">AP10*1.01</f>
-        <v>487.83</v>
+        <f t="shared" si="25"/>
+        <v>829.57</v>
       </c>
       <c r="AR10" s="6">
-        <f t="shared" si="33"/>
-        <v>492.70830000000001</v>
+        <f t="shared" ref="AR10:AU10" si="41">AQ10*1.01</f>
+        <v>837.86570000000006</v>
       </c>
       <c r="AS10" s="6">
-        <f t="shared" si="33"/>
-        <v>497.63538299999999</v>
+        <f t="shared" si="41"/>
+        <v>846.24435700000004</v>
       </c>
       <c r="AT10" s="6">
-        <f t="shared" si="33"/>
-        <v>502.61173682999998</v>
+        <f t="shared" si="41"/>
+        <v>854.70680057000004</v>
       </c>
       <c r="AU10" s="6">
-        <f t="shared" si="33"/>
-        <v>507.63785419829998</v>
+        <f t="shared" si="41"/>
+        <v>863.25386857570004</v>
       </c>
       <c r="AV10" s="6">
-        <f t="shared" si="27"/>
-        <v>512.71423274028302</v>
+        <f t="shared" si="34"/>
+        <v>871.88640726145707</v>
       </c>
       <c r="AW10" s="6">
-        <f t="shared" si="27"/>
-        <v>517.84137506768582</v>
+        <f t="shared" si="34"/>
+        <v>880.60527133407163</v>
       </c>
       <c r="AX10" s="6">
-        <f t="shared" si="28"/>
-        <v>523.01978881836271</v>
+        <f t="shared" si="35"/>
+        <v>889.41132404741234</v>
       </c>
       <c r="AY10" s="6">
-        <f t="shared" si="29"/>
-        <v>528.24998670654634</v>
+        <f t="shared" si="36"/>
+        <v>898.30543728788643</v>
       </c>
       <c r="AZ10" s="6">
-        <f t="shared" si="30"/>
-        <v>533.53248657361178</v>
+        <f t="shared" si="37"/>
+        <v>907.28849166076532</v>
       </c>
       <c r="BA10" s="6">
-        <f t="shared" si="31"/>
-        <v>538.86781143934786</v>
+        <f t="shared" si="38"/>
+        <v>916.36137657737299</v>
       </c>
     </row>
     <row r="11" spans="2:53" x14ac:dyDescent="0.3">
@@ -2470,7 +2553,7 @@
         <v>-135</v>
       </c>
       <c r="R11" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-312</v>
       </c>
       <c r="S11" s="6">
@@ -2483,7 +2566,7 @@
         <v>-719</v>
       </c>
       <c r="V11" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-236</v>
       </c>
       <c r="W11" s="6">
@@ -2496,7 +2579,7 @@
         <v>-833</v>
       </c>
       <c r="Z11" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-253</v>
       </c>
       <c r="AA11" s="6">
@@ -2509,13 +2592,23 @@
         <v>-476</v>
       </c>
       <c r="AD11" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>259</v>
       </c>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="6"/>
+      <c r="AE11" s="6">
+        <v>-385</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>-185</v>
+      </c>
+      <c r="AG11" s="6">
+        <f t="shared" si="39"/>
+        <v>-480.76</v>
+      </c>
+      <c r="AH11" s="6">
+        <f t="shared" si="39"/>
+        <v>261.58999999999997</v>
+      </c>
       <c r="AJ11" s="6"/>
       <c r="AK11" s="6"/>
       <c r="AL11" s="6"/>
@@ -2532,48 +2625,48 @@
         <v>-1138</v>
       </c>
       <c r="AQ11" s="6">
-        <f t="shared" ref="AQ11:BA11" si="34">AP11*1.01</f>
-        <v>-1149.3800000000001</v>
+        <f t="shared" si="25"/>
+        <v>-789.17000000000007</v>
       </c>
       <c r="AR11" s="6">
+        <f t="shared" ref="AR11:AU11" si="42">AQ11*1.01</f>
+        <v>-797.06170000000009</v>
+      </c>
+      <c r="AS11" s="6">
+        <f t="shared" si="42"/>
+        <v>-805.03231700000015</v>
+      </c>
+      <c r="AT11" s="6">
+        <f t="shared" si="42"/>
+        <v>-813.0826401700001</v>
+      </c>
+      <c r="AU11" s="6">
+        <f t="shared" si="42"/>
+        <v>-821.21346657170011</v>
+      </c>
+      <c r="AV11" s="6">
         <f t="shared" si="34"/>
-        <v>-1160.8738000000001</v>
-      </c>
-      <c r="AS11" s="6">
+        <v>-829.42560123741714</v>
+      </c>
+      <c r="AW11" s="6">
         <f t="shared" si="34"/>
-        <v>-1172.482538</v>
-      </c>
-      <c r="AT11" s="6">
-        <f t="shared" si="34"/>
-        <v>-1184.2073633800001</v>
-      </c>
-      <c r="AU11" s="6">
-        <f t="shared" si="34"/>
-        <v>-1196.0494370138001</v>
-      </c>
-      <c r="AV11" s="6">
-        <f t="shared" si="27"/>
-        <v>-1208.0099313839382</v>
-      </c>
-      <c r="AW11" s="6">
-        <f t="shared" si="27"/>
-        <v>-1220.0900306977776</v>
+        <v>-837.71985724979129</v>
       </c>
       <c r="AX11" s="6">
-        <f t="shared" si="28"/>
-        <v>-1232.2909310047553</v>
+        <f t="shared" si="35"/>
+        <v>-846.09705582228924</v>
       </c>
       <c r="AY11" s="6">
-        <f t="shared" si="29"/>
-        <v>-1244.6138403148029</v>
+        <f t="shared" si="36"/>
+        <v>-854.55802638051216</v>
       </c>
       <c r="AZ11" s="6">
-        <f t="shared" si="30"/>
-        <v>-1257.059978717951</v>
+        <f t="shared" si="37"/>
+        <v>-863.10360664431732</v>
       </c>
       <c r="BA11" s="6">
-        <f t="shared" si="31"/>
-        <v>-1269.6305785051306</v>
+        <f t="shared" si="38"/>
+        <v>-871.73464271076045</v>
       </c>
     </row>
     <row r="12" spans="2:53" x14ac:dyDescent="0.3">
@@ -2602,7 +2695,7 @@
         <v>72</v>
       </c>
       <c r="R12" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-10</v>
       </c>
       <c r="S12" s="6">
@@ -2615,7 +2708,7 @@
         <v>-58</v>
       </c>
       <c r="V12" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>-14</v>
       </c>
       <c r="W12" s="6">
@@ -2628,7 +2721,7 @@
         <v>-36</v>
       </c>
       <c r="Z12" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>-10</v>
       </c>
       <c r="AA12" s="6">
@@ -2641,13 +2734,23 @@
         <v>90</v>
       </c>
       <c r="AD12" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>-52</v>
       </c>
-      <c r="AE12" s="6"/>
-      <c r="AF12" s="6"/>
-      <c r="AG12" s="6"/>
-      <c r="AH12" s="6"/>
+      <c r="AE12" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF12" s="6">
+        <v>-100</v>
+      </c>
+      <c r="AG12" s="6">
+        <f t="shared" si="39"/>
+        <v>90.9</v>
+      </c>
+      <c r="AH12" s="6">
+        <f t="shared" si="39"/>
+        <v>-52.52</v>
+      </c>
       <c r="AJ12" s="6"/>
       <c r="AK12" s="6"/>
       <c r="AL12" s="6"/>
@@ -2664,48 +2767,48 @@
         <v>37</v>
       </c>
       <c r="AQ12" s="6">
-        <f t="shared" ref="AQ12:BA12" si="35">AP12*1.01</f>
-        <v>37.369999999999997</v>
+        <f t="shared" si="25"/>
+        <v>-45.62</v>
       </c>
       <c r="AR12" s="6">
+        <f t="shared" ref="AR12:AU12" si="43">AQ12*1.01</f>
+        <v>-46.0762</v>
+      </c>
+      <c r="AS12" s="6">
+        <f t="shared" si="43"/>
+        <v>-46.536962000000003</v>
+      </c>
+      <c r="AT12" s="6">
+        <f t="shared" si="43"/>
+        <v>-47.00233162</v>
+      </c>
+      <c r="AU12" s="6">
+        <f t="shared" si="43"/>
+        <v>-47.472354936199999</v>
+      </c>
+      <c r="AV12" s="6">
+        <f t="shared" si="34"/>
+        <v>-47.947078485562002</v>
+      </c>
+      <c r="AW12" s="6">
+        <f t="shared" si="34"/>
+        <v>-48.426549270417624</v>
+      </c>
+      <c r="AX12" s="6">
         <f t="shared" si="35"/>
-        <v>37.743699999999997</v>
-      </c>
-      <c r="AS12" s="6">
-        <f t="shared" si="35"/>
-        <v>38.121136999999997</v>
-      </c>
-      <c r="AT12" s="6">
-        <f t="shared" si="35"/>
-        <v>38.50234837</v>
-      </c>
-      <c r="AU12" s="6">
-        <f t="shared" si="35"/>
-        <v>38.887371853700003</v>
-      </c>
-      <c r="AV12" s="6">
-        <f t="shared" si="27"/>
-        <v>39.276245572237002</v>
-      </c>
-      <c r="AW12" s="6">
-        <f t="shared" si="27"/>
-        <v>39.669008027959372</v>
-      </c>
-      <c r="AX12" s="6">
-        <f t="shared" si="28"/>
-        <v>40.065698108238962</v>
+        <v>-48.910814763121799</v>
       </c>
       <c r="AY12" s="6">
-        <f t="shared" si="29"/>
-        <v>40.466355089321354</v>
+        <f t="shared" si="36"/>
+        <v>-49.39992291075302</v>
       </c>
       <c r="AZ12" s="6">
-        <f t="shared" si="30"/>
-        <v>40.871018640214565</v>
+        <f t="shared" si="37"/>
+        <v>-49.89392213986055</v>
       </c>
       <c r="BA12" s="6">
-        <f t="shared" si="31"/>
-        <v>41.279728826616712</v>
+        <f t="shared" si="38"/>
+        <v>-50.392861361259158</v>
       </c>
     </row>
     <row r="13" spans="2:53" x14ac:dyDescent="0.3">
@@ -2765,69 +2868,81 @@
         <v>2685</v>
       </c>
       <c r="P13" s="6">
-        <f t="shared" ref="P13:AD13" si="36">SUM(P6:P12)</f>
+        <f t="shared" ref="P13:AD13" si="44">SUM(P6:P12)</f>
         <v>3528</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>3876</v>
       </c>
       <c r="R13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>4558</v>
       </c>
       <c r="S13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>2735</v>
       </c>
       <c r="T13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>3880</v>
       </c>
       <c r="U13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>3586</v>
       </c>
       <c r="V13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>3361</v>
       </c>
       <c r="W13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>3946</v>
       </c>
       <c r="X13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>3969</v>
       </c>
       <c r="Y13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>3192</v>
       </c>
       <c r="Z13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>3612</v>
       </c>
       <c r="AA13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>3243</v>
       </c>
       <c r="AB13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>3787</v>
       </c>
       <c r="AC13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>3695</v>
       </c>
       <c r="AD13" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>4252</v>
       </c>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
+      <c r="AE13" s="6">
+        <f t="shared" ref="AE13:AH13" si="45">SUM(AE6:AE12)</f>
+        <v>4275</v>
+      </c>
+      <c r="AF13" s="6">
+        <f t="shared" si="45"/>
+        <v>4169</v>
+      </c>
+      <c r="AG13" s="6">
+        <f t="shared" si="45"/>
+        <v>3806.0024000000008</v>
+      </c>
+      <c r="AH13" s="6">
+        <f t="shared" si="45"/>
+        <v>4297.1249999999991</v>
+      </c>
       <c r="AJ13" s="6">
         <f>SUM(C13:F13)</f>
         <v>-1734</v>
@@ -2845,60 +2960,60 @@
         <v>14647</v>
       </c>
       <c r="AN13" s="6">
-        <f t="shared" ref="AN13:AP13" si="37">SUM(AN6:AN12)</f>
+        <f t="shared" ref="AN13:AP13" si="46">SUM(AN6:AN12)</f>
         <v>13562</v>
       </c>
       <c r="AO13" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>14719</v>
       </c>
       <c r="AP13" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>14977</v>
       </c>
       <c r="AQ13" s="6">
-        <f t="shared" ref="AQ13" si="38">SUM(AQ6:AQ12)</f>
-        <v>14551.4478</v>
+        <f t="shared" ref="AQ13" si="47">SUM(AQ6:AQ12)</f>
+        <v>16547.127400000001</v>
       </c>
       <c r="AR13" s="6">
-        <f t="shared" ref="AR13" si="39">SUM(AR6:AR12)</f>
-        <v>14865.629478000004</v>
+        <f t="shared" ref="AR13" si="48">SUM(AR6:AR12)</f>
+        <v>16171.175348999999</v>
       </c>
       <c r="AS13" s="6">
-        <f t="shared" ref="AS13" si="40">SUM(AS6:AS12)</f>
-        <v>15101.149380780003</v>
+        <f t="shared" ref="AS13" si="49">SUM(AS6:AS12)</f>
+        <v>16514.001460980002</v>
       </c>
       <c r="AT13" s="6">
-        <f t="shared" ref="AT13" si="41">SUM(AT6:AT12)</f>
-        <v>15340.761754747802</v>
+        <f t="shared" ref="AT13" si="50">SUM(AT6:AT12)</f>
+        <v>16770.916428469805</v>
       </c>
       <c r="AU13" s="6">
-        <f t="shared" ref="AU13" si="42">SUM(AU6:AU12)</f>
-        <v>15584.542270058482</v>
+        <f t="shared" ref="AU13" si="51">SUM(AU6:AU12)</f>
+        <v>17032.236044692105</v>
       </c>
       <c r="AV13" s="6">
-        <f t="shared" ref="AV13" si="43">SUM(AV6:AV12)</f>
-        <v>15769.136505141847</v>
+        <f t="shared" ref="AV13" si="52">SUM(AV6:AV12)</f>
+        <v>17229.69344700587</v>
       </c>
       <c r="AW13" s="6">
-        <f t="shared" ref="AW13" si="44">SUM(AW6:AW12)</f>
-        <v>15956.151658823706</v>
+        <f t="shared" ref="AW13" si="53">SUM(AW6:AW12)</f>
+        <v>17401.990381475931</v>
       </c>
       <c r="AX13" s="6">
-        <f t="shared" ref="AX13" si="45">SUM(AX6:AX12)</f>
-        <v>16145.623439814994</v>
+        <f t="shared" ref="AX13" si="54">SUM(AX6:AX12)</f>
+        <v>17576.010285290682</v>
       </c>
       <c r="AY13" s="6">
-        <f t="shared" ref="AY13" si="46">SUM(AY6:AY12)</f>
-        <v>16337.588143904251</v>
+        <f t="shared" ref="AY13" si="55">SUM(AY6:AY12)</f>
+        <v>17751.770388143592</v>
       </c>
       <c r="AZ13" s="6">
-        <f t="shared" ref="AZ13" si="47">SUM(AZ6:AZ12)</f>
-        <v>16532.082664428224</v>
+        <f t="shared" ref="AZ13" si="56">SUM(AZ6:AZ12)</f>
+        <v>17929.288092025032</v>
       </c>
       <c r="BA13" s="6">
-        <f t="shared" ref="BA13" si="48">SUM(BA6:BA12)</f>
-        <v>16729.14450293914</v>
+        <f t="shared" ref="BA13" si="57">SUM(BA6:BA12)</f>
+        <v>18108.580972945281</v>
       </c>
     </row>
     <row r="14" spans="2:53" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2910,47 +3025,47 @@
         <v>3331</v>
       </c>
       <c r="D14" s="8">
-        <f t="shared" ref="D14:N14" si="49">D5-SUM(D6:D13)</f>
+        <f t="shared" ref="D14:N14" si="58">D5-SUM(D6:D13)</f>
         <v>2636</v>
       </c>
       <c r="E14" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>2485</v>
       </c>
       <c r="F14" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>2665</v>
       </c>
       <c r="G14" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>2798</v>
       </c>
       <c r="H14" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>-1558</v>
       </c>
       <c r="I14" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>2690</v>
       </c>
       <c r="J14" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>383</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>617</v>
       </c>
       <c r="L14" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>-1682</v>
       </c>
       <c r="M14" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>3070</v>
       </c>
       <c r="N14" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>4598</v>
       </c>
       <c r="O14" s="8">
@@ -2958,79 +3073,91 @@
         <v>4701</v>
       </c>
       <c r="P14" s="8">
-        <f t="shared" ref="P14:AD14" si="50">P5-P13</f>
+        <f t="shared" ref="P14:AD14" si="59">P5-P13</f>
         <v>4374</v>
       </c>
       <c r="Q14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>2838</v>
       </c>
       <c r="R14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>4115</v>
       </c>
       <c r="S14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>5229</v>
       </c>
       <c r="T14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>4622</v>
       </c>
       <c r="U14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>5196</v>
       </c>
       <c r="V14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>5411</v>
       </c>
       <c r="W14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>5504</v>
       </c>
       <c r="X14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>4988</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>4842</v>
       </c>
       <c r="Z14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>4326</v>
       </c>
       <c r="AA14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>3863</v>
       </c>
       <c r="AB14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>4037</v>
       </c>
       <c r="AC14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>2517</v>
       </c>
       <c r="AD14" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>3438</v>
       </c>
-      <c r="AE14" s="8"/>
-      <c r="AF14" s="8"/>
-      <c r="AG14" s="8"/>
-      <c r="AH14" s="8"/>
+      <c r="AE14" s="8">
+        <f t="shared" ref="AE14:AH14" si="60">AE5-AE13</f>
+        <v>2289</v>
+      </c>
+      <c r="AF14" s="8">
+        <f t="shared" si="60"/>
+        <v>1273</v>
+      </c>
+      <c r="AG14" s="8">
+        <f t="shared" si="60"/>
+        <v>2685.2615999999994</v>
+      </c>
+      <c r="AH14" s="8">
+        <f t="shared" si="60"/>
+        <v>3162.1750000000011</v>
+      </c>
       <c r="AJ14" s="8">
-        <f t="shared" ref="AJ14:AP14" si="51">AJ5-AJ6-AJ7-AJ8-AJ13</f>
+        <f t="shared" ref="AJ14:AL14" si="61">AJ5-AJ6-AJ7-AJ8-AJ13</f>
         <v>11117</v>
       </c>
       <c r="AK14" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v>4313</v>
       </c>
       <c r="AL14" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v>6603</v>
       </c>
       <c r="AM14" s="8">
@@ -3038,60 +3165,60 @@
         <v>16028</v>
       </c>
       <c r="AN14" s="8">
-        <f t="shared" ref="AN14:AP14" si="52">AN5-AN13</f>
+        <f t="shared" ref="AN14:AP14" si="62">AN5-AN13</f>
         <v>20458</v>
       </c>
       <c r="AO14" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>19660</v>
       </c>
       <c r="AP14" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>13599</v>
       </c>
       <c r="AQ14" s="8">
-        <f t="shared" ref="AQ14" si="53">AQ5-AQ13</f>
-        <v>15411.797399999998</v>
+        <f t="shared" ref="AQ14" si="63">AQ5-AQ13</f>
+        <v>9409.4366000000118</v>
       </c>
       <c r="AR14" s="8">
-        <f t="shared" ref="AR14" si="54">AR5-AR13</f>
-        <v>15397.248173999995</v>
+        <f t="shared" ref="AR14" si="64">AR5-AR13</f>
+        <v>13273.704717000002</v>
       </c>
       <c r="AS14" s="8">
-        <f t="shared" ref="AS14" si="55">AS5-AS13</f>
-        <v>15464.357047739995</v>
+        <f t="shared" ref="AS14" si="65">AS5-AS13</f>
+        <v>13519.77620634</v>
       </c>
       <c r="AT14" s="8">
-        <f t="shared" ref="AT14" si="56">AT5-AT13</f>
-        <v>15530.399738057398</v>
+        <f t="shared" ref="AT14" si="66">AT5-AT13</f>
+        <v>15007.680703332604</v>
       </c>
       <c r="AU14" s="8">
-        <f t="shared" ref="AU14" si="57">AU5-AU13</f>
-        <v>15595.330837674766</v>
+        <f t="shared" ref="AU14" si="67">AU5-AU13</f>
+        <v>15064.147058428327</v>
       </c>
       <c r="AV14" s="8">
-        <f t="shared" ref="AV14" si="58">AV5-AV13</f>
-        <v>15722.535333668733</v>
+        <f t="shared" ref="AV14" si="68">AV5-AV13</f>
+        <v>15187.653487145766</v>
       </c>
       <c r="AW14" s="8">
-        <f t="shared" ref="AW14" si="59">AW5-AW13</f>
-        <v>15850.436898374985</v>
+        <f t="shared" ref="AW14" si="69">AW5-AW13</f>
+        <v>15339.530022017221</v>
       </c>
       <c r="AX14" s="8">
-        <f t="shared" ref="AX14" si="60">AX5-AX13</f>
-        <v>15979.031002955686</v>
+        <f t="shared" ref="AX14" si="70">AX5-AX13</f>
+        <v>15492.925322237399</v>
       </c>
       <c r="AY14" s="8">
-        <f t="shared" ref="AY14" si="61">AY5-AY13</f>
-        <v>16108.312843294132</v>
+        <f t="shared" ref="AY14" si="71">AY5-AY13</f>
+        <v>15647.854575459776</v>
       </c>
       <c r="AZ14" s="8">
-        <f t="shared" ref="AZ14" si="62">AZ5-AZ13</f>
-        <v>16238.277332642141</v>
+        <f t="shared" ref="AZ14" si="72">AZ5-AZ13</f>
+        <v>15804.333121214368</v>
       </c>
       <c r="BA14" s="8">
-        <f t="shared" ref="BA14" si="63">BA5-BA13</f>
-        <v>16368.919094101933</v>
+        <f t="shared" ref="BA14" si="73">BA5-BA13</f>
+        <v>15962.376452426513</v>
       </c>
     </row>
     <row r="15" spans="2:53" x14ac:dyDescent="0.3">
@@ -3189,10 +3316,20 @@
         <f>AP15-AC15-AB15-AA15</f>
         <v>-188</v>
       </c>
-      <c r="AE15" s="6"/>
-      <c r="AF15" s="6"/>
-      <c r="AG15" s="6"/>
-      <c r="AH15" s="6"/>
+      <c r="AE15" s="6">
+        <v>-180</v>
+      </c>
+      <c r="AF15" s="6">
+        <v>-156</v>
+      </c>
+      <c r="AG15" s="6">
+        <f t="shared" ref="AG15:AG16" si="74">AC15*1.01</f>
+        <v>-166.65</v>
+      </c>
+      <c r="AH15" s="6">
+        <f t="shared" ref="AH15:AH16" si="75">AD15*1.01</f>
+        <v>-189.88</v>
+      </c>
       <c r="AJ15" s="6">
         <f>SUM(C15:F15)</f>
         <v>-271</v>
@@ -3217,48 +3354,48 @@
         <v>-738</v>
       </c>
       <c r="AQ15" s="6">
-        <f t="shared" ref="AQ15:AW15" si="64">AP15*1.02</f>
-        <v>-752.76</v>
+        <f t="shared" ref="AQ15:AQ16" si="76">SUM(AE15:AH15)</f>
+        <v>-692.53</v>
       </c>
       <c r="AR15" s="6">
-        <f t="shared" si="64"/>
-        <v>-767.8152</v>
+        <f t="shared" ref="AR15:AW15" si="77">AQ15*1.02</f>
+        <v>-706.38059999999996</v>
       </c>
       <c r="AS15" s="6">
-        <f t="shared" si="64"/>
-        <v>-783.17150400000003</v>
+        <f t="shared" si="77"/>
+        <v>-720.50821199999996</v>
       </c>
       <c r="AT15" s="6">
-        <f t="shared" si="64"/>
-        <v>-798.83493408000004</v>
+        <f t="shared" si="77"/>
+        <v>-734.91837623999993</v>
       </c>
       <c r="AU15" s="6">
-        <f t="shared" si="64"/>
-        <v>-814.81163276160009</v>
+        <f t="shared" si="77"/>
+        <v>-749.61674376479993</v>
       </c>
       <c r="AV15" s="6">
-        <f t="shared" si="64"/>
-        <v>-831.10786541683206</v>
+        <f t="shared" si="77"/>
+        <v>-764.60907864009596</v>
       </c>
       <c r="AW15" s="6">
-        <f t="shared" si="64"/>
-        <v>-847.73002272516874</v>
+        <f t="shared" si="77"/>
+        <v>-779.90126021289791</v>
       </c>
       <c r="AX15" s="6">
-        <f t="shared" ref="AX15" si="65">AW15*1.02</f>
-        <v>-864.68462317967214</v>
+        <f t="shared" ref="AX15" si="78">AW15*1.02</f>
+        <v>-795.49928541715587</v>
       </c>
       <c r="AY15" s="6">
-        <f t="shared" ref="AY15" si="66">AX15*1.02</f>
-        <v>-881.97831564326555</v>
+        <f t="shared" ref="AY15" si="79">AX15*1.02</f>
+        <v>-811.409271125499</v>
       </c>
       <c r="AZ15" s="6">
-        <f t="shared" ref="AZ15" si="67">AY15*1.02</f>
-        <v>-899.61788195613087</v>
+        <f t="shared" ref="AZ15" si="80">AY15*1.02</f>
+        <v>-827.63745654800903</v>
       </c>
       <c r="BA15" s="6">
-        <f t="shared" ref="BA15" si="68">AZ15*1.02</f>
-        <v>-917.61023959525346</v>
+        <f t="shared" ref="BA15" si="81">AZ15*1.02</f>
+        <v>-844.19020567896928</v>
       </c>
     </row>
     <row r="16" spans="2:53" x14ac:dyDescent="0.3">
@@ -3356,10 +3493,20 @@
         <f>AP16-AC16-AB16-AA16</f>
         <v>63</v>
       </c>
-      <c r="AE16" s="6"/>
-      <c r="AF16" s="6"/>
-      <c r="AG16" s="6"/>
-      <c r="AH16" s="6"/>
+      <c r="AE16" s="6">
+        <v>47</v>
+      </c>
+      <c r="AF16" s="6">
+        <v>27</v>
+      </c>
+      <c r="AG16" s="6">
+        <f t="shared" si="74"/>
+        <v>37.369999999999997</v>
+      </c>
+      <c r="AH16" s="6">
+        <f t="shared" si="75"/>
+        <v>63.63</v>
+      </c>
       <c r="AJ16" s="6">
         <f>SUM(C16:F16)</f>
         <v>793</v>
@@ -3384,48 +3531,48 @@
         <v>190</v>
       </c>
       <c r="AQ16" s="6">
-        <f>AP16*1.03</f>
-        <v>195.70000000000002</v>
+        <f t="shared" si="76"/>
+        <v>175</v>
       </c>
       <c r="AR16" s="6">
-        <f t="shared" ref="AR16:AW16" si="69">AQ16*1.03</f>
-        <v>201.57100000000003</v>
+        <f t="shared" ref="AR16:AW16" si="82">AQ16*1.03</f>
+        <v>180.25</v>
       </c>
       <c r="AS16" s="6">
-        <f t="shared" si="69"/>
-        <v>207.61813000000004</v>
+        <f t="shared" si="82"/>
+        <v>185.6575</v>
       </c>
       <c r="AT16" s="6">
-        <f t="shared" si="69"/>
-        <v>213.84667390000004</v>
+        <f t="shared" si="82"/>
+        <v>191.227225</v>
       </c>
       <c r="AU16" s="6">
-        <f t="shared" si="69"/>
-        <v>220.26207411700005</v>
+        <f t="shared" si="82"/>
+        <v>196.96404175000001</v>
       </c>
       <c r="AV16" s="6">
-        <f t="shared" si="69"/>
-        <v>226.86993634051007</v>
+        <f t="shared" si="82"/>
+        <v>202.8729630025</v>
       </c>
       <c r="AW16" s="6">
-        <f t="shared" si="69"/>
-        <v>233.67603443072537</v>
+        <f t="shared" si="82"/>
+        <v>208.95915189257499</v>
       </c>
       <c r="AX16" s="6">
-        <f t="shared" ref="AX16:BA16" si="70">AW16*1.03</f>
-        <v>240.68631546364713</v>
+        <f t="shared" ref="AX16:BA16" si="83">AW16*1.03</f>
+        <v>215.22792644935225</v>
       </c>
       <c r="AY16" s="6">
-        <f t="shared" si="70"/>
-        <v>247.90690492755655</v>
+        <f t="shared" si="83"/>
+        <v>221.68476424283281</v>
       </c>
       <c r="AZ16" s="6">
-        <f t="shared" si="70"/>
-        <v>255.34411207538326</v>
+        <f t="shared" si="83"/>
+        <v>228.3353071701178</v>
       </c>
       <c r="BA16" s="6">
-        <f t="shared" si="70"/>
-        <v>263.00443543764476</v>
+        <f t="shared" si="83"/>
+        <v>235.18536638522133</v>
       </c>
     </row>
     <row r="17" spans="2:132" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3433,121 +3580,133 @@
         <v>21</v>
       </c>
       <c r="C17" s="8">
-        <f t="shared" ref="C17:N17" si="71">C14-C15-C16</f>
+        <f t="shared" ref="C17:N17" si="84">C14-C15-C16</f>
         <v>3247</v>
       </c>
       <c r="D17" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="84"/>
         <v>2530</v>
       </c>
       <c r="E17" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="84"/>
         <v>2345</v>
       </c>
       <c r="F17" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="84"/>
         <v>2473</v>
       </c>
       <c r="G17" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="84"/>
         <v>2623</v>
       </c>
       <c r="H17" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="84"/>
         <v>-1672</v>
       </c>
       <c r="I17" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="84"/>
         <v>2575</v>
       </c>
       <c r="J17" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="84"/>
         <v>304</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="84"/>
         <v>540</v>
       </c>
       <c r="L17" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="84"/>
         <v>-1742</v>
       </c>
       <c r="M17" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="84"/>
         <v>3032</v>
       </c>
       <c r="N17" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="84"/>
         <v>4509</v>
       </c>
       <c r="O17" s="8">
-        <f t="shared" ref="O17:P17" si="72">O14-O15-O16</f>
+        <f t="shared" ref="O17:P17" si="85">O14-O15-O16</f>
         <v>4658</v>
       </c>
       <c r="P17" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="85"/>
         <v>4304</v>
       </c>
       <c r="Q17" s="8">
-        <f t="shared" ref="Q17:R17" si="73">Q14-Q15-Q16</f>
+        <f t="shared" ref="Q17:R17" si="86">Q14-Q15-Q16</f>
         <v>2819</v>
       </c>
       <c r="R17" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="86"/>
         <v>4030</v>
       </c>
       <c r="S17" s="8">
-        <f t="shared" ref="S17:T17" si="74">S14-S15-S16</f>
+        <f t="shared" ref="S17:T17" si="87">S14-S15-S16</f>
         <v>5187</v>
       </c>
       <c r="T17" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="87"/>
         <v>4549</v>
       </c>
       <c r="U17" s="8">
-        <f t="shared" ref="U17:V17" si="75">U14-U15-U16</f>
+        <f t="shared" ref="U17:V17" si="88">U14-U15-U16</f>
         <v>5166</v>
       </c>
       <c r="V17" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="88"/>
         <v>5402</v>
       </c>
       <c r="W17" s="8">
-        <f t="shared" ref="W17:X17" si="76">W14-W15-W16</f>
+        <f t="shared" ref="W17:X17" si="89">W14-W15-W16</f>
         <v>5569</v>
       </c>
       <c r="X17" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="89"/>
         <v>5085</v>
       </c>
       <c r="Y17" s="8">
-        <f t="shared" ref="Y17:AD17" si="77">Y14-Y15-Y16</f>
+        <f t="shared" ref="Y17:AD17" si="90">Y14-Y15-Y16</f>
         <v>4980</v>
       </c>
       <c r="Z17" s="8">
-        <f t="shared" ref="Z17" si="78">Z14-Z15-Z16</f>
+        <f t="shared" ref="Z17" si="91">Z14-Z15-Z16</f>
         <v>4450</v>
       </c>
       <c r="AA17" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="90"/>
         <v>4029</v>
       </c>
       <c r="AB17" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="90"/>
         <v>4166</v>
       </c>
       <c r="AC17" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="90"/>
         <v>2645</v>
       </c>
       <c r="AD17" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="90"/>
         <v>3563</v>
       </c>
-      <c r="AE17" s="8"/>
-      <c r="AF17" s="8"/>
-      <c r="AG17" s="8"/>
-      <c r="AH17" s="8"/>
+      <c r="AE17" s="8">
+        <f t="shared" ref="AE17:AH17" si="92">AE14-AE15-AE16</f>
+        <v>2422</v>
+      </c>
+      <c r="AF17" s="8">
+        <f t="shared" si="92"/>
+        <v>1402</v>
+      </c>
+      <c r="AG17" s="8">
+        <f t="shared" si="92"/>
+        <v>2814.5415999999996</v>
+      </c>
+      <c r="AH17" s="8">
+        <f t="shared" si="92"/>
+        <v>3288.4250000000011</v>
+      </c>
       <c r="AJ17" s="8">
         <f>AJ14-AJ15-AJ16</f>
         <v>10595</v>
@@ -3561,64 +3720,64 @@
         <v>6339</v>
       </c>
       <c r="AM17" s="8">
-        <f t="shared" ref="AM17" si="79">AM14-AM15-AM16</f>
+        <f t="shared" ref="AM17" si="93">AM14-AM15-AM16</f>
         <v>15811</v>
       </c>
       <c r="AN17" s="8">
-        <f t="shared" ref="AN17:AV17" si="80">AN14-AN15-AN16</f>
+        <f t="shared" ref="AN17:AV17" si="94">AN14-AN15-AN16</f>
         <v>20304</v>
       </c>
       <c r="AO17" s="8">
-        <f t="shared" ref="AO17:AP17" si="81">AO14-AO15-AO16</f>
+        <f t="shared" ref="AO17:AP17" si="95">AO14-AO15-AO16</f>
         <v>20084</v>
       </c>
       <c r="AP17" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="95"/>
         <v>14147</v>
       </c>
       <c r="AQ17" s="8">
-        <f t="shared" si="80"/>
-        <v>15968.857399999997</v>
+        <f t="shared" si="94"/>
+        <v>9926.9666000000125</v>
       </c>
       <c r="AR17" s="8">
-        <f t="shared" si="80"/>
-        <v>15963.492373999994</v>
+        <f t="shared" si="94"/>
+        <v>13799.835317000003</v>
       </c>
       <c r="AS17" s="8">
-        <f t="shared" si="80"/>
-        <v>16039.910421739994</v>
+        <f t="shared" si="94"/>
+        <v>14054.626918340002</v>
       </c>
       <c r="AT17" s="8">
-        <f t="shared" si="80"/>
-        <v>16115.387998237398</v>
+        <f t="shared" si="94"/>
+        <v>15551.371854572604</v>
       </c>
       <c r="AU17" s="8">
-        <f t="shared" si="80"/>
-        <v>16189.880396319368</v>
+        <f t="shared" si="94"/>
+        <v>15616.799760443128</v>
       </c>
       <c r="AV17" s="8">
-        <f t="shared" si="80"/>
-        <v>16326.773262745053</v>
+        <f t="shared" si="94"/>
+        <v>15749.389602783362</v>
       </c>
       <c r="AW17" s="8">
-        <f t="shared" ref="AW17:BA17" si="82">AW14-AW15-AW16</f>
-        <v>16464.490886669428</v>
+        <f t="shared" ref="AW17:BA17" si="96">AW14-AW15-AW16</f>
+        <v>15910.472130337545</v>
       </c>
       <c r="AX17" s="8">
-        <f t="shared" si="82"/>
-        <v>16603.029310671711</v>
+        <f t="shared" si="96"/>
+        <v>16073.196681205203</v>
       </c>
       <c r="AY17" s="8">
-        <f t="shared" si="82"/>
-        <v>16742.384254009841</v>
+        <f t="shared" si="96"/>
+        <v>16237.579082342443</v>
       </c>
       <c r="AZ17" s="8">
-        <f t="shared" si="82"/>
-        <v>16882.551102522888</v>
+        <f t="shared" si="96"/>
+        <v>16403.635270592258</v>
       </c>
       <c r="BA17" s="8">
-        <f t="shared" si="82"/>
-        <v>17023.524898259544</v>
+        <f t="shared" si="96"/>
+        <v>16571.381291720263</v>
       </c>
     </row>
     <row r="18" spans="2:132" x14ac:dyDescent="0.3">
@@ -3713,13 +3872,23 @@
         <v>926</v>
       </c>
       <c r="AD18" s="6">
-        <f t="shared" ref="AD18:AD19" si="83">AP18-AC18-AB18-AA18</f>
+        <f t="shared" ref="AD18:AD19" si="97">AP18-AC18-AB18-AA18</f>
         <v>704</v>
       </c>
-      <c r="AE18" s="6"/>
-      <c r="AF18" s="6"/>
-      <c r="AG18" s="6"/>
-      <c r="AH18" s="6"/>
+      <c r="AE18" s="6">
+        <v>691</v>
+      </c>
+      <c r="AF18" s="6">
+        <v>445</v>
+      </c>
+      <c r="AG18" s="6">
+        <f t="shared" ref="AG18:AH18" si="98">AG17*0.28</f>
+        <v>788.07164799999998</v>
+      </c>
+      <c r="AH18" s="6">
+        <f t="shared" si="98"/>
+        <v>920.75900000000036</v>
+      </c>
       <c r="AJ18" s="6">
         <f>SUM(C18:F18)</f>
         <v>3013</v>
@@ -3744,48 +3913,48 @@
         <v>3738</v>
       </c>
       <c r="AQ18" s="6">
-        <f>AQ17*0.28</f>
-        <v>4471.2800719999996</v>
+        <f t="shared" ref="AQ18:AQ19" si="99">SUM(AE18:AH18)</f>
+        <v>2844.8306480000006</v>
       </c>
       <c r="AR18" s="6">
-        <f t="shared" ref="AR18:AW18" si="84">AR17*0.28</f>
-        <v>4469.7778647199984</v>
+        <f t="shared" ref="AR18:AW18" si="100">AR17*0.28</f>
+        <v>3863.9538887600011</v>
       </c>
       <c r="AS18" s="6">
-        <f t="shared" si="84"/>
-        <v>4491.1749180871993</v>
+        <f t="shared" si="100"/>
+        <v>3935.2955371352009</v>
       </c>
       <c r="AT18" s="6">
-        <f t="shared" si="84"/>
-        <v>4512.308639506472</v>
+        <f t="shared" si="100"/>
+        <v>4354.3841192803293</v>
       </c>
       <c r="AU18" s="6">
-        <f t="shared" si="84"/>
-        <v>4533.1665109694231</v>
+        <f t="shared" si="100"/>
+        <v>4372.7039329240761</v>
       </c>
       <c r="AV18" s="6">
-        <f t="shared" si="84"/>
-        <v>4571.4965135686152</v>
+        <f t="shared" si="100"/>
+        <v>4409.8290887793419</v>
       </c>
       <c r="AW18" s="6">
-        <f t="shared" si="84"/>
-        <v>4610.0574482674401</v>
+        <f t="shared" si="100"/>
+        <v>4454.9321964945129</v>
       </c>
       <c r="AX18" s="6">
-        <f t="shared" ref="AX18" si="85">AX17*0.28</f>
-        <v>4648.8482069880793</v>
+        <f t="shared" ref="AX18" si="101">AX17*0.28</f>
+        <v>4500.4950707374574</v>
       </c>
       <c r="AY18" s="6">
-        <f t="shared" ref="AY18" si="86">AY17*0.28</f>
-        <v>4687.8675911227556</v>
+        <f t="shared" ref="AY18" si="102">AY17*0.28</f>
+        <v>4546.522143055885</v>
       </c>
       <c r="AZ18" s="6">
-        <f t="shared" ref="AZ18" si="87">AZ17*0.28</f>
-        <v>4727.1143087064092</v>
+        <f t="shared" ref="AZ18" si="103">AZ17*0.28</f>
+        <v>4593.0178757658323</v>
       </c>
       <c r="BA18" s="6">
-        <f t="shared" ref="BA18" si="88">BA17*0.28</f>
-        <v>4766.5869715126728</v>
+        <f t="shared" ref="BA18" si="104">BA17*0.28</f>
+        <v>4639.9867616816737</v>
       </c>
     </row>
     <row r="19" spans="2:132" x14ac:dyDescent="0.3">
@@ -3880,13 +4049,23 @@
         <v>-14</v>
       </c>
       <c r="AD19" s="6">
-        <f t="shared" si="83"/>
+        <f t="shared" si="97"/>
         <v>119</v>
       </c>
-      <c r="AE19" s="6"/>
-      <c r="AF19" s="6"/>
-      <c r="AG19" s="6"/>
-      <c r="AH19" s="6"/>
+      <c r="AE19" s="6">
+        <v>53</v>
+      </c>
+      <c r="AF19" s="6">
+        <v>42</v>
+      </c>
+      <c r="AG19" s="6">
+        <f t="shared" ref="AG19:AH19" si="105">AG17*0.02</f>
+        <v>56.290831999999995</v>
+      </c>
+      <c r="AH19" s="6">
+        <f t="shared" si="105"/>
+        <v>65.768500000000017</v>
+      </c>
       <c r="AJ19" s="6">
         <f>SUM(C19:F19)</f>
         <v>333</v>
@@ -3911,48 +4090,48 @@
         <v>202</v>
       </c>
       <c r="AQ19" s="6">
-        <f t="shared" ref="AQ19:AW19" si="89">AP19*1.05</f>
-        <v>212.10000000000002</v>
+        <f t="shared" si="99"/>
+        <v>217.05933200000001</v>
       </c>
       <c r="AR19" s="6">
-        <f t="shared" si="89"/>
-        <v>222.70500000000004</v>
+        <f t="shared" ref="AR19:AW19" si="106">AQ19*1.05</f>
+        <v>227.91229860000001</v>
       </c>
       <c r="AS19" s="6">
-        <f t="shared" si="89"/>
-        <v>233.84025000000005</v>
+        <f t="shared" si="106"/>
+        <v>239.30791353000004</v>
       </c>
       <c r="AT19" s="6">
-        <f t="shared" si="89"/>
-        <v>245.53226250000006</v>
+        <f t="shared" si="106"/>
+        <v>251.27330920650004</v>
       </c>
       <c r="AU19" s="6">
-        <f t="shared" si="89"/>
-        <v>257.8088756250001</v>
+        <f t="shared" si="106"/>
+        <v>263.83697466682509</v>
       </c>
       <c r="AV19" s="6">
-        <f t="shared" si="89"/>
-        <v>270.69931940625014</v>
+        <f t="shared" si="106"/>
+        <v>277.02882340016635</v>
       </c>
       <c r="AW19" s="6">
-        <f t="shared" si="89"/>
-        <v>284.23428537656264</v>
+        <f t="shared" si="106"/>
+        <v>290.88026457017469</v>
       </c>
       <c r="AX19" s="6">
-        <f t="shared" ref="AX19" si="90">AW19*1.05</f>
-        <v>298.44599964539077</v>
+        <f t="shared" ref="AX19" si="107">AW19*1.05</f>
+        <v>305.42427779868342</v>
       </c>
       <c r="AY19" s="6">
-        <f t="shared" ref="AY19" si="91">AX19*1.05</f>
-        <v>313.36829962766035</v>
+        <f t="shared" ref="AY19" si="108">AX19*1.05</f>
+        <v>320.69549168861761</v>
       </c>
       <c r="AZ19" s="6">
-        <f t="shared" ref="AZ19" si="92">AY19*1.05</f>
-        <v>329.03671460904337</v>
+        <f t="shared" ref="AZ19" si="109">AY19*1.05</f>
+        <v>336.73026627304853</v>
       </c>
       <c r="BA19" s="6">
-        <f t="shared" ref="BA19" si="93">AZ19*1.05</f>
-        <v>345.48855033949553</v>
+        <f t="shared" ref="BA19" si="110">AZ19*1.05</f>
+        <v>353.56677958670099</v>
       </c>
     </row>
     <row r="20" spans="2:132" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3960,121 +4139,133 @@
         <v>26</v>
       </c>
       <c r="C20" s="8">
-        <f t="shared" ref="C20:L20" si="94">C17-C18-C19</f>
+        <f t="shared" ref="C20:L20" si="111">C17-C18-C19</f>
         <v>2273</v>
       </c>
       <c r="D20" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>1726</v>
       </c>
       <c r="E20" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>1689</v>
       </c>
       <c r="F20" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>1561</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>2095</v>
       </c>
       <c r="H20" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>-1328</v>
       </c>
       <c r="I20" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>1719</v>
       </c>
       <c r="J20" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>-109</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>94</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="111"/>
         <v>-2001</v>
       </c>
       <c r="M20" s="8">
-        <f t="shared" ref="M20:N20" si="95">M17-M18-M19</f>
+        <f t="shared" ref="M20:N20" si="112">M17-M18-M19</f>
         <v>2049</v>
       </c>
       <c r="N20" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="112"/>
         <v>3485</v>
       </c>
       <c r="O20" s="8">
-        <f t="shared" ref="O20:P20" si="96">O17-O18-O19</f>
+        <f t="shared" ref="O20:P20" si="113">O17-O18-O19</f>
         <v>3387</v>
       </c>
       <c r="P20" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="113"/>
         <v>3033</v>
       </c>
       <c r="Q20" s="8">
-        <f t="shared" ref="Q20:R20" si="97">Q17-Q18-Q19</f>
+        <f t="shared" ref="Q20:R20" si="114">Q17-Q18-Q19</f>
         <v>1861</v>
       </c>
       <c r="R20" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="114"/>
         <v>2379</v>
       </c>
       <c r="S20" s="8">
-        <f t="shared" ref="S20:T20" si="98">S17-S18-S19</f>
+        <f t="shared" ref="S20:T20" si="115">S17-S18-S19</f>
         <v>3490</v>
       </c>
       <c r="T20" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="115"/>
         <v>3107</v>
       </c>
       <c r="U20" s="8">
-        <f t="shared" ref="U20:V20" si="99">U17-U18-U19</f>
+        <f t="shared" ref="U20:V20" si="116">U17-U18-U19</f>
         <v>3923</v>
       </c>
       <c r="V20" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="116"/>
         <v>3981</v>
       </c>
       <c r="W20" s="8">
-        <f t="shared" ref="W20:X20" si="100">W17-W18-W19</f>
+        <f t="shared" ref="W20:X20" si="117">W17-W18-W19</f>
         <v>3945</v>
       </c>
       <c r="X20" s="8">
-        <f t="shared" si="100"/>
+        <f t="shared" si="117"/>
         <v>3563</v>
       </c>
       <c r="Y20" s="8">
-        <f t="shared" ref="Y20:AA20" si="101">Y17-Y18-Y19</f>
+        <f t="shared" ref="Y20:AA20" si="118">Y17-Y18-Y19</f>
         <v>3636</v>
       </c>
       <c r="Z20" s="8">
-        <f t="shared" ref="Z20" si="102">Z17-Z18-Z19</f>
+        <f t="shared" ref="Z20" si="119">Z17-Z18-Z19</f>
         <v>3117</v>
       </c>
       <c r="AA20" s="8">
-        <f t="shared" si="101"/>
+        <f t="shared" si="118"/>
         <v>2974</v>
       </c>
       <c r="AB20" s="8">
-        <f t="shared" ref="AB20:AD20" si="103">AB17-AB18-AB19</f>
+        <f t="shared" ref="AB20:AD20" si="120">AB17-AB18-AB19</f>
         <v>3016</v>
       </c>
       <c r="AC20" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="120"/>
         <v>1733</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="120"/>
         <v>2740</v>
       </c>
-      <c r="AE20" s="8"/>
-      <c r="AF20" s="8"/>
-      <c r="AG20" s="8"/>
-      <c r="AH20" s="8"/>
+      <c r="AE20" s="8">
+        <f t="shared" ref="AE20:AH20" si="121">AE17-AE18-AE19</f>
+        <v>1678</v>
+      </c>
+      <c r="AF20" s="8">
+        <f t="shared" si="121"/>
+        <v>915</v>
+      </c>
+      <c r="AG20" s="8">
+        <f t="shared" si="121"/>
+        <v>1970.1791199999996</v>
+      </c>
+      <c r="AH20" s="8">
+        <f t="shared" si="121"/>
+        <v>2301.8975000000005</v>
+      </c>
       <c r="AJ20" s="8">
         <f>AJ17-AJ18-AJ19</f>
         <v>7249</v>
@@ -4088,380 +4279,380 @@
         <v>3627</v>
       </c>
       <c r="AM20" s="8">
-        <f t="shared" ref="AM20" si="104">AM17-AM18-AM19</f>
+        <f t="shared" ref="AM20" si="122">AM17-AM18-AM19</f>
         <v>10660</v>
       </c>
       <c r="AN20" s="8">
-        <f t="shared" ref="AN20:AV20" si="105">AN17-AN18-AN19</f>
+        <f t="shared" ref="AN20:AV20" si="123">AN17-AN18-AN19</f>
         <v>14501</v>
       </c>
       <c r="AO20" s="8">
-        <f t="shared" ref="AO20:AP20" si="106">AO17-AO18-AO19</f>
+        <f t="shared" ref="AO20:AP20" si="124">AO17-AO18-AO19</f>
         <v>14261</v>
       </c>
       <c r="AP20" s="8">
-        <f t="shared" si="106"/>
+        <f t="shared" si="124"/>
         <v>10207</v>
       </c>
       <c r="AQ20" s="8">
-        <f t="shared" si="105"/>
-        <v>11285.477327999997</v>
+        <f t="shared" si="123"/>
+        <v>6865.0766200000116</v>
       </c>
       <c r="AR20" s="8">
-        <f t="shared" si="105"/>
-        <v>11271.009509279995</v>
+        <f t="shared" si="123"/>
+        <v>9707.9691296400015</v>
       </c>
       <c r="AS20" s="8">
-        <f t="shared" si="105"/>
-        <v>11314.895253652796</v>
+        <f t="shared" si="123"/>
+        <v>9880.0234676748005</v>
       </c>
       <c r="AT20" s="8">
-        <f t="shared" si="105"/>
-        <v>11357.547096230926</v>
+        <f t="shared" si="123"/>
+        <v>10945.714426085773</v>
       </c>
       <c r="AU20" s="8">
-        <f t="shared" si="105"/>
-        <v>11398.905009724946</v>
+        <f t="shared" si="123"/>
+        <v>10980.258852852226</v>
       </c>
       <c r="AV20" s="8">
-        <f t="shared" si="105"/>
-        <v>11484.577429770188</v>
+        <f t="shared" si="123"/>
+        <v>11062.531690603855</v>
       </c>
       <c r="AW20" s="8">
-        <f t="shared" ref="AW20:BA20" si="107">AW17-AW18-AW19</f>
-        <v>11570.199153025425</v>
+        <f t="shared" ref="AW20:BA20" si="125">AW17-AW18-AW19</f>
+        <v>11164.659669272858</v>
       </c>
       <c r="AX20" s="8">
-        <f t="shared" si="107"/>
-        <v>11655.73510403824</v>
+        <f t="shared" si="125"/>
+        <v>11267.277332669062</v>
       </c>
       <c r="AY20" s="8">
-        <f t="shared" si="107"/>
-        <v>11741.148363259426</v>
+        <f t="shared" si="125"/>
+        <v>11370.361447597941</v>
       </c>
       <c r="AZ20" s="8">
-        <f t="shared" si="107"/>
-        <v>11826.400079207437</v>
+        <f t="shared" si="125"/>
+        <v>11473.887128553377</v>
       </c>
       <c r="BA20" s="8">
-        <f t="shared" si="107"/>
-        <v>11911.449376407376</v>
+        <f t="shared" si="125"/>
+        <v>11577.827750451888</v>
       </c>
       <c r="BB20" s="3">
         <f>BA20*(1+$BD$26)</f>
-        <v>11792.334882643301</v>
+        <v>11462.049472947368</v>
       </c>
       <c r="BC20" s="3">
-        <f t="shared" ref="BC20:DN20" si="108">BB20*(1+$BD$26)</f>
-        <v>11674.411533816869</v>
+        <f t="shared" ref="BC20:DN20" si="126">BB20*(1+$BD$26)</f>
+        <v>11347.428978217895</v>
       </c>
       <c r="BD20" s="3">
-        <f t="shared" si="108"/>
-        <v>11557.667418478699</v>
+        <f t="shared" si="126"/>
+        <v>11233.954688435715</v>
       </c>
       <c r="BE20" s="3">
-        <f t="shared" si="108"/>
-        <v>11442.090744293911</v>
+        <f t="shared" si="126"/>
+        <v>11121.615141551358</v>
       </c>
       <c r="BF20" s="3">
-        <f t="shared" si="108"/>
-        <v>11327.669836850971</v>
+        <f t="shared" si="126"/>
+        <v>11010.398990135844</v>
       </c>
       <c r="BG20" s="3">
-        <f t="shared" si="108"/>
-        <v>11214.393138482461</v>
+        <f t="shared" si="126"/>
+        <v>10900.295000234486</v>
       </c>
       <c r="BH20" s="3">
-        <f t="shared" si="108"/>
-        <v>11102.249207097637</v>
+        <f t="shared" si="126"/>
+        <v>10791.292050232141</v>
       </c>
       <c r="BI20" s="3">
-        <f t="shared" si="108"/>
-        <v>10991.22671502666</v>
+        <f t="shared" si="126"/>
+        <v>10683.379129729819</v>
       </c>
       <c r="BJ20" s="3">
-        <f t="shared" si="108"/>
-        <v>10881.314447876393</v>
+        <f t="shared" si="126"/>
+        <v>10576.545338432521</v>
       </c>
       <c r="BK20" s="3">
-        <f t="shared" si="108"/>
-        <v>10772.50130339763</v>
+        <f t="shared" si="126"/>
+        <v>10470.779885048196</v>
       </c>
       <c r="BL20" s="3">
-        <f t="shared" si="108"/>
-        <v>10664.776290363654</v>
+        <f t="shared" si="126"/>
+        <v>10366.072086197713</v>
       </c>
       <c r="BM20" s="3">
-        <f t="shared" si="108"/>
-        <v>10558.128527460018</v>
+        <f t="shared" si="126"/>
+        <v>10262.411365335736</v>
       </c>
       <c r="BN20" s="3">
-        <f t="shared" si="108"/>
-        <v>10452.547242185417</v>
+        <f t="shared" si="126"/>
+        <v>10159.787251682379</v>
       </c>
       <c r="BO20" s="3">
-        <f t="shared" si="108"/>
-        <v>10348.021769763563</v>
+        <f t="shared" si="126"/>
+        <v>10058.189379165555</v>
       </c>
       <c r="BP20" s="3">
-        <f t="shared" si="108"/>
-        <v>10244.541552065928</v>
+        <f t="shared" si="126"/>
+        <v>9957.6074853738992</v>
       </c>
       <c r="BQ20" s="3">
-        <f t="shared" si="108"/>
-        <v>10142.096136545269</v>
+        <f t="shared" si="126"/>
+        <v>9858.0314105201596</v>
       </c>
       <c r="BR20" s="3">
-        <f t="shared" si="108"/>
-        <v>10040.675175179817</v>
+        <f t="shared" si="126"/>
+        <v>9759.4510964149576</v>
       </c>
       <c r="BS20" s="3">
-        <f t="shared" si="108"/>
-        <v>9940.2684234280187</v>
+        <f t="shared" si="126"/>
+        <v>9661.8565854508088</v>
       </c>
       <c r="BT20" s="3">
-        <f t="shared" si="108"/>
-        <v>9840.8657391937377</v>
+        <f t="shared" si="126"/>
+        <v>9565.2380195963015</v>
       </c>
       <c r="BU20" s="3">
-        <f t="shared" si="108"/>
-        <v>9742.4570818018001</v>
+        <f t="shared" si="126"/>
+        <v>9469.5856394003386</v>
       </c>
       <c r="BV20" s="3">
-        <f t="shared" si="108"/>
-        <v>9645.0325109837813</v>
+        <f t="shared" si="126"/>
+        <v>9374.8897830063343</v>
       </c>
       <c r="BW20" s="3">
-        <f t="shared" si="108"/>
-        <v>9548.5821858739437</v>
+        <f t="shared" si="126"/>
+        <v>9281.1408851762717</v>
       </c>
       <c r="BX20" s="3">
-        <f t="shared" si="108"/>
-        <v>9453.096364015204</v>
+        <f t="shared" si="126"/>
+        <v>9188.3294763245085</v>
       </c>
       <c r="BY20" s="3">
-        <f t="shared" si="108"/>
-        <v>9358.5654003750515</v>
+        <f t="shared" si="126"/>
+        <v>9096.4461815612631</v>
       </c>
       <c r="BZ20" s="3">
-        <f t="shared" si="108"/>
-        <v>9264.9797463713003</v>
+        <f t="shared" si="126"/>
+        <v>9005.4817197456505</v>
       </c>
       <c r="CA20" s="3">
-        <f t="shared" si="108"/>
-        <v>9172.3299489075871</v>
+        <f t="shared" si="126"/>
+        <v>8915.4269025481935</v>
       </c>
       <c r="CB20" s="3">
-        <f t="shared" si="108"/>
-        <v>9080.6066494185106</v>
+        <f t="shared" si="126"/>
+        <v>8826.2726335227107</v>
       </c>
       <c r="CC20" s="3">
-        <f t="shared" si="108"/>
-        <v>8989.8005829243248</v>
+        <f t="shared" si="126"/>
+        <v>8738.0099071874829</v>
       </c>
       <c r="CD20" s="3">
-        <f t="shared" si="108"/>
-        <v>8899.9025770950811</v>
+        <f t="shared" si="126"/>
+        <v>8650.6298081156074</v>
       </c>
       <c r="CE20" s="3">
-        <f t="shared" si="108"/>
-        <v>8810.9035513241306</v>
+        <f t="shared" si="126"/>
+        <v>8564.1235100344511</v>
       </c>
       <c r="CF20" s="3">
-        <f t="shared" si="108"/>
-        <v>8722.7945158108887</v>
+        <f t="shared" si="126"/>
+        <v>8478.4822749341074</v>
       </c>
       <c r="CG20" s="3">
-        <f t="shared" si="108"/>
-        <v>8635.5665706527798</v>
+        <f t="shared" si="126"/>
+        <v>8393.697452184766</v>
       </c>
       <c r="CH20" s="3">
-        <f t="shared" si="108"/>
-        <v>8549.2109049462524</v>
+        <f t="shared" si="126"/>
+        <v>8309.7604776629178</v>
       </c>
       <c r="CI20" s="3">
-        <f t="shared" si="108"/>
-        <v>8463.7187958967897</v>
+        <f t="shared" si="126"/>
+        <v>8226.6628728862888</v>
       </c>
       <c r="CJ20" s="3">
-        <f t="shared" si="108"/>
-        <v>8379.0816079378219</v>
+        <f t="shared" si="126"/>
+        <v>8144.3962441574258</v>
       </c>
       <c r="CK20" s="3">
-        <f t="shared" si="108"/>
-        <v>8295.2907918584442</v>
+        <f t="shared" si="126"/>
+        <v>8062.9522817158513</v>
       </c>
       <c r="CL20" s="3">
-        <f t="shared" si="108"/>
-        <v>8212.3378839398592</v>
+        <f t="shared" si="126"/>
+        <v>7982.3227588986929</v>
       </c>
       <c r="CM20" s="3">
-        <f t="shared" si="108"/>
-        <v>8130.2145051004609</v>
+        <f t="shared" si="126"/>
+        <v>7902.4995313097061</v>
       </c>
       <c r="CN20" s="3">
-        <f t="shared" si="108"/>
-        <v>8048.9123600494559</v>
+        <f t="shared" si="126"/>
+        <v>7823.4745359966091</v>
       </c>
       <c r="CO20" s="3">
-        <f t="shared" si="108"/>
-        <v>7968.4232364489608</v>
+        <f t="shared" si="126"/>
+        <v>7745.2397906366432</v>
       </c>
       <c r="CP20" s="3">
-        <f t="shared" si="108"/>
-        <v>7888.7390040844712</v>
+        <f t="shared" si="126"/>
+        <v>7667.7873927302771</v>
       </c>
       <c r="CQ20" s="3">
-        <f t="shared" si="108"/>
-        <v>7809.8516140436268</v>
+        <f t="shared" si="126"/>
+        <v>7591.109518802974</v>
       </c>
       <c r="CR20" s="3">
-        <f t="shared" si="108"/>
-        <v>7731.7530979031908</v>
+        <f t="shared" si="126"/>
+        <v>7515.1984236149437</v>
       </c>
       <c r="CS20" s="3">
-        <f t="shared" si="108"/>
-        <v>7654.4355669241586</v>
+        <f t="shared" si="126"/>
+        <v>7440.0464393787943</v>
       </c>
       <c r="CT20" s="3">
-        <f t="shared" si="108"/>
-        <v>7577.8912112549169</v>
+        <f t="shared" si="126"/>
+        <v>7365.6459749850064</v>
       </c>
       <c r="CU20" s="3">
-        <f t="shared" si="108"/>
-        <v>7502.1122991423681</v>
+        <f t="shared" si="126"/>
+        <v>7291.9895152351564</v>
       </c>
       <c r="CV20" s="3">
-        <f t="shared" si="108"/>
-        <v>7427.0911761509442</v>
+        <f t="shared" si="126"/>
+        <v>7219.0696200828052</v>
       </c>
       <c r="CW20" s="3">
-        <f t="shared" si="108"/>
-        <v>7352.8202643894347</v>
+        <f t="shared" si="126"/>
+        <v>7146.8789238819772</v>
       </c>
       <c r="CX20" s="3">
-        <f t="shared" si="108"/>
-        <v>7279.2920617455402</v>
+        <f t="shared" si="126"/>
+        <v>7075.4101346431571</v>
       </c>
       <c r="CY20" s="3">
-        <f t="shared" si="108"/>
-        <v>7206.4991411280844</v>
+        <f t="shared" si="126"/>
+        <v>7004.6560332967256</v>
       </c>
       <c r="CZ20" s="3">
-        <f t="shared" si="108"/>
-        <v>7134.4341497168034</v>
+        <f t="shared" si="126"/>
+        <v>6934.609472963758</v>
       </c>
       <c r="DA20" s="3">
-        <f t="shared" si="108"/>
-        <v>7063.0898082196354</v>
+        <f t="shared" si="126"/>
+        <v>6865.26337823412</v>
       </c>
       <c r="DB20" s="3">
-        <f t="shared" si="108"/>
-        <v>6992.4589101374386</v>
+        <f t="shared" si="126"/>
+        <v>6796.6107444517784</v>
       </c>
       <c r="DC20" s="3">
-        <f t="shared" si="108"/>
-        <v>6922.5343210360643</v>
+        <f t="shared" si="126"/>
+        <v>6728.6446370072608</v>
       </c>
       <c r="DD20" s="3">
-        <f t="shared" si="108"/>
-        <v>6853.3089778257036</v>
+        <f t="shared" si="126"/>
+        <v>6661.3581906371883</v>
       </c>
       <c r="DE20" s="3">
-        <f t="shared" si="108"/>
-        <v>6784.7758880474466</v>
+        <f t="shared" si="126"/>
+        <v>6594.7446087308163</v>
       </c>
       <c r="DF20" s="3">
-        <f t="shared" si="108"/>
-        <v>6716.9281291669722</v>
+        <f t="shared" si="126"/>
+        <v>6528.7971626435083</v>
       </c>
       <c r="DG20" s="3">
-        <f t="shared" si="108"/>
-        <v>6649.7588478753023</v>
+        <f t="shared" si="126"/>
+        <v>6463.5091910170731</v>
       </c>
       <c r="DH20" s="3">
-        <f t="shared" si="108"/>
-        <v>6583.2612593965496</v>
+        <f t="shared" si="126"/>
+        <v>6398.8740991069026</v>
       </c>
       <c r="DI20" s="3">
-        <f t="shared" si="108"/>
-        <v>6517.4286468025839</v>
+        <f t="shared" si="126"/>
+        <v>6334.8853581158337</v>
       </c>
       <c r="DJ20" s="3">
-        <f t="shared" si="108"/>
-        <v>6452.2543603345584</v>
+        <f t="shared" si="126"/>
+        <v>6271.5365045346753</v>
       </c>
       <c r="DK20" s="3">
-        <f t="shared" si="108"/>
-        <v>6387.7318167312123</v>
+        <f t="shared" si="126"/>
+        <v>6208.8211394893287</v>
       </c>
       <c r="DL20" s="3">
-        <f t="shared" si="108"/>
-        <v>6323.8544985639001</v>
+        <f t="shared" si="126"/>
+        <v>6146.732928094435</v>
       </c>
       <c r="DM20" s="3">
-        <f t="shared" si="108"/>
-        <v>6260.6159535782608</v>
+        <f t="shared" si="126"/>
+        <v>6085.2655988134902</v>
       </c>
       <c r="DN20" s="3">
-        <f t="shared" si="108"/>
-        <v>6198.0097940424785</v>
+        <f t="shared" si="126"/>
+        <v>6024.4129428253555</v>
       </c>
       <c r="DO20" s="3">
-        <f t="shared" ref="DO20:EB20" si="109">DN20*(1+$BD$26)</f>
-        <v>6136.029696102054</v>
+        <f t="shared" ref="DO20:EB20" si="127">DN20*(1+$BD$26)</f>
+        <v>5964.168813397102</v>
       </c>
       <c r="DP20" s="3">
-        <f t="shared" si="109"/>
-        <v>6074.6693991410339</v>
+        <f t="shared" si="127"/>
+        <v>5904.527125263131</v>
       </c>
       <c r="DQ20" s="3">
-        <f t="shared" si="109"/>
-        <v>6013.9227051496237</v>
+        <f t="shared" si="127"/>
+        <v>5845.4818540104998</v>
       </c>
       <c r="DR20" s="3">
-        <f t="shared" si="109"/>
-        <v>5953.7834780981275</v>
+        <f t="shared" si="127"/>
+        <v>5787.0270354703944</v>
       </c>
       <c r="DS20" s="3">
-        <f t="shared" si="109"/>
-        <v>5894.2456433171465</v>
+        <f t="shared" si="127"/>
+        <v>5729.1567651156902</v>
       </c>
       <c r="DT20" s="3">
-        <f t="shared" si="109"/>
-        <v>5835.3031868839753</v>
+        <f t="shared" si="127"/>
+        <v>5671.8651974645336</v>
       </c>
       <c r="DU20" s="3">
-        <f t="shared" si="109"/>
-        <v>5776.9501550151354</v>
+        <f t="shared" si="127"/>
+        <v>5615.146545489888</v>
       </c>
       <c r="DV20" s="3">
-        <f t="shared" si="109"/>
-        <v>5719.1806534649841</v>
+        <f t="shared" si="127"/>
+        <v>5558.9950800349889</v>
       </c>
       <c r="DW20" s="3">
-        <f t="shared" si="109"/>
-        <v>5661.9888469303341</v>
+        <f t="shared" si="127"/>
+        <v>5503.4051292346385</v>
       </c>
       <c r="DX20" s="3">
-        <f t="shared" si="109"/>
-        <v>5605.3689584610311</v>
+        <f t="shared" si="127"/>
+        <v>5448.3710779422918</v>
       </c>
       <c r="DY20" s="3">
-        <f t="shared" si="109"/>
-        <v>5549.3152688764203</v>
+        <f t="shared" si="127"/>
+        <v>5393.8873671628689</v>
       </c>
       <c r="DZ20" s="3">
-        <f t="shared" si="109"/>
-        <v>5493.8221161876563</v>
+        <f t="shared" si="127"/>
+        <v>5339.9484934912398</v>
       </c>
       <c r="EA20" s="3">
-        <f t="shared" si="109"/>
-        <v>5438.8838950257796</v>
+        <f t="shared" si="127"/>
+        <v>5286.549008556327</v>
       </c>
       <c r="EB20" s="3">
-        <f t="shared" si="109"/>
-        <v>5384.4950560755215</v>
+        <f t="shared" si="127"/>
+        <v>5233.6835184707634</v>
       </c>
     </row>
     <row r="21" spans="2:132" x14ac:dyDescent="0.3">
@@ -4552,10 +4743,18 @@
       <c r="AD21" s="6">
         <v>1013.6</v>
       </c>
-      <c r="AE21" s="6"/>
-      <c r="AF21" s="6"/>
-      <c r="AG21" s="6"/>
-      <c r="AH21" s="6"/>
+      <c r="AE21" s="6">
+        <v>1013.6</v>
+      </c>
+      <c r="AF21" s="6">
+        <v>1013.6</v>
+      </c>
+      <c r="AG21" s="6">
+        <v>1013.6</v>
+      </c>
+      <c r="AH21" s="6">
+        <v>1013.6</v>
+      </c>
       <c r="AJ21" s="6">
         <v>1069.8</v>
       </c>
@@ -4616,121 +4815,133 @@
         <v>27</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:L22" si="110">C20/C21</f>
+        <f t="shared" ref="C22:L22" si="128">C20/C21</f>
         <v>2.124696204898112</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="128"/>
         <v>1.6133856795662742</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="128"/>
         <v>1.5787997756590018</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="128"/>
         <v>1.4591512432230325</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="128"/>
         <v>1.958309964479342</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="128"/>
         <v>-1.2413535240231819</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="128"/>
         <v>1.6068424004486821</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="128"/>
         <v>-0.10188820340250515</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="128"/>
         <v>8.7866891007664982E-2</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="128"/>
         <v>-1.870443073471677</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" ref="M22:N22" si="111">M20/M21</f>
+        <f t="shared" ref="M22:N22" si="129">M20/M21</f>
         <v>1.9153112731351656</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="129"/>
         <v>3.2576182464011967</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22:P22" si="112">O20/O21</f>
+        <f t="shared" ref="O22:P22" si="130">O20/O21</f>
         <v>3.1660123387549075</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="130"/>
         <v>2.8351093662366798</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22:R22" si="113">Q20/Q21</f>
+        <f t="shared" ref="Q22:R22" si="131">Q20/Q21</f>
         <v>1.7395774911198356</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="131"/>
         <v>2.2237801458216491</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22:T22" si="114">S20/S21</f>
+        <f t="shared" ref="S22:T22" si="132">S20/S21</f>
         <v>3.2622920171994765</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="132"/>
         <v>2.9042811740512247</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22:V22" si="115">U20/U21</f>
+        <f t="shared" ref="U22:V22" si="133">U20/U21</f>
         <v>3.6670405683305294</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="133"/>
         <v>3.721256309590578</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" ref="W22:X22" si="116">W20/W21</f>
+        <f t="shared" ref="W22:X22" si="134">W20/W21</f>
         <v>3.6876051598429616</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="134"/>
         <v>3.3305290708543653</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" ref="Y22:AA22" si="117">Y20/Y21</f>
+        <f t="shared" ref="Y22:AA22" si="135">Y20/Y21</f>
         <v>3.3987661245092542</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22" si="118">Z20/Z21</f>
+        <f t="shared" ref="Z22" si="136">Z20/Z21</f>
         <v>2.9136287156477847</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="135"/>
         <v>2.8640215716486899</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" ref="AB22:AD22" si="119">AB20/AB21</f>
+        <f t="shared" ref="AB22:AD22" si="137">AB20/AB21</f>
         <v>2.9044684129429887</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="137"/>
         <v>1.7097474348855564</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="137"/>
         <v>2.7032359905288081</v>
       </c>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="9"/>
-      <c r="AG22" s="9"/>
-      <c r="AH22" s="9"/>
+      <c r="AE22" s="9">
+        <f t="shared" ref="AE22:AH22" si="138">AE20/AE21</f>
+        <v>1.6554853985793212</v>
+      </c>
+      <c r="AF22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.90272296764009474</v>
+      </c>
+      <c r="AG22" s="9">
+        <f t="shared" si="138"/>
+        <v>1.9437441988950273</v>
+      </c>
+      <c r="AH22" s="9">
+        <f t="shared" si="138"/>
+        <v>2.2710117403314922</v>
+      </c>
       <c r="AJ22" s="9">
         <f>AJ20/AJ21</f>
         <v>6.7760329033464206</v>
@@ -4744,64 +4955,64 @@
         <v>3.3903533370723502</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" ref="AM22" si="120">AM20/AM21</f>
+        <f t="shared" ref="AM22" si="139">AM20/AM21</f>
         <v>10.265793528505393</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" ref="AN22:AV22" si="121">AN20/AN21</f>
+        <f t="shared" ref="AN22:AV22" si="140">AN20/AN21</f>
         <v>13.964753466872109</v>
       </c>
       <c r="AO22" s="9">
-        <f t="shared" ref="AO22:AP22" si="122">AO20/AO21</f>
+        <f t="shared" ref="AO22:AP22" si="141">AO20/AO21</f>
         <v>13.733628659476116</v>
       </c>
       <c r="AP22" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="141"/>
         <v>10.070047355958957</v>
       </c>
       <c r="AQ22" s="9">
-        <f t="shared" si="121"/>
-        <v>11.134054191002365</v>
+        <f t="shared" si="140"/>
+        <v>6.7729643054459467</v>
       </c>
       <c r="AR22" s="9">
-        <f t="shared" si="121"/>
-        <v>11.119780494554059</v>
+        <f t="shared" si="140"/>
+        <v>9.5777122431333872</v>
       </c>
       <c r="AS22" s="9">
-        <f t="shared" si="121"/>
-        <v>11.163077400999207</v>
+        <f t="shared" si="140"/>
+        <v>9.7474580383531961</v>
       </c>
       <c r="AT22" s="9">
-        <f t="shared" si="121"/>
-        <v>11.205156961553795</v>
+        <f t="shared" si="140"/>
+        <v>10.798850065199066</v>
       </c>
       <c r="AU22" s="9">
-        <f t="shared" si="121"/>
-        <v>11.245959954345842</v>
+        <f t="shared" si="140"/>
+        <v>10.832930991369599</v>
       </c>
       <c r="AV22" s="9">
-        <f t="shared" si="121"/>
-        <v>11.330482862835623</v>
+        <f t="shared" si="140"/>
+        <v>10.914099931534979</v>
       </c>
       <c r="AW22" s="9">
-        <f t="shared" ref="AW22:BA22" si="123">AW20/AW21</f>
-        <v>11.41495575476068</v>
+        <f t="shared" ref="AW22:BA22" si="142">AW20/AW21</f>
+        <v>11.014857605833521</v>
       </c>
       <c r="AX22" s="9">
-        <f t="shared" si="123"/>
-        <v>11.499344025294238</v>
+        <f t="shared" si="142"/>
+        <v>11.11609839450381</v>
       </c>
       <c r="AY22" s="9">
-        <f t="shared" si="123"/>
-        <v>11.583611250255945</v>
+        <f t="shared" si="142"/>
+        <v>11.217799376083208</v>
       </c>
       <c r="AZ22" s="9">
-        <f t="shared" si="123"/>
-        <v>11.66771909945485</v>
+        <f t="shared" si="142"/>
+        <v>11.31993599896742</v>
       </c>
       <c r="BA22" s="9">
-        <f t="shared" si="123"/>
-        <v>11.751627245863631</v>
+        <f t="shared" si="142"/>
+        <v>11.422481995315596</v>
       </c>
     </row>
     <row r="24" spans="2:132" x14ac:dyDescent="0.3">
@@ -4813,35 +5024,35 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="10">
-        <f t="shared" ref="G24:N24" si="124">G3/C3-1</f>
+        <f t="shared" ref="G24:N24" si="143">G3/C3-1</f>
         <v>-2.1867538016840937E-3</v>
       </c>
       <c r="H24" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="143"/>
         <v>4.6471685150652586E-2</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="143"/>
         <v>7.6073711173559433E-2</v>
       </c>
       <c r="J24" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="143"/>
         <v>1.1092040334692133E-2</v>
       </c>
       <c r="K24" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="143"/>
         <v>-6.2345710111340602E-2</v>
       </c>
       <c r="L24" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="143"/>
         <v>-0.29228604923798363</v>
       </c>
       <c r="M24" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="143"/>
         <v>-6.9077883059856737E-2</v>
       </c>
       <c r="N24" s="10">
-        <f t="shared" si="124"/>
+        <f t="shared" si="143"/>
         <v>-1.0736944851146846E-2</v>
       </c>
       <c r="O24" s="10"/>
@@ -4849,57 +5060,69 @@
       <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
       <c r="S24" s="10">
-        <f t="shared" ref="S24:AD24" si="125">S3/O3-1</f>
+        <f t="shared" ref="S24:AE24" si="144">S3/O3-1</f>
         <v>6.0093668268353495E-2</v>
       </c>
       <c r="T24" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="144"/>
         <v>6.7870120736138739E-2</v>
       </c>
       <c r="U24" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="144"/>
         <v>0.19177173191771724</v>
       </c>
       <c r="V24" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="144"/>
         <v>0.16353575482406346</v>
       </c>
       <c r="W24" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="144"/>
         <v>7.6252223305984357E-2</v>
       </c>
       <c r="X24" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="144"/>
         <v>4.9423710208561955E-2</v>
       </c>
       <c r="Y24" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="144"/>
         <v>-1.3681196309258681E-2</v>
       </c>
       <c r="Z24" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="144"/>
         <v>-1.8096236860717485E-2</v>
       </c>
       <c r="AA24" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="144"/>
         <v>-4.3794647617016791E-2</v>
       </c>
       <c r="AB24" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="144"/>
         <v>-3.9172615778876096E-2</v>
       </c>
       <c r="AC24" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="144"/>
         <v>-7.1827956989247266E-2</v>
       </c>
       <c r="AD24" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="144"/>
         <v>-4.498149574029453E-2</v>
       </c>
-      <c r="AE24" s="10"/>
-      <c r="AF24" s="10"/>
-      <c r="AG24" s="10"/>
-      <c r="AH24" s="10"/>
+      <c r="AE24" s="10">
+        <f t="shared" si="144"/>
+        <v>-7.3843837983999072E-2</v>
+      </c>
+      <c r="AF24" s="10">
+        <f t="shared" ref="AF24" si="145">AF3/AB3-1</f>
+        <v>-9.7705685436681788E-2</v>
+      </c>
+      <c r="AG24" s="10">
+        <f t="shared" ref="AG24" si="146">AG3/AC3-1</f>
+        <v>-6.0000000000000053E-2</v>
+      </c>
+      <c r="AH24" s="10">
+        <f t="shared" ref="AH24" si="147">AH3/AD3-1</f>
+        <v>-3.0000000000000027E-2</v>
+      </c>
       <c r="AI24" s="3"/>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="10">
@@ -4912,59 +5135,59 @@
       </c>
       <c r="AM24" s="10"/>
       <c r="AN24" s="10">
-        <f t="shared" ref="AN24:AW24" si="126">AN3/AM3-1</f>
+        <f t="shared" ref="AN24:AW24" si="148">AN3/AM3-1</f>
         <v>0.12042451808533672</v>
       </c>
       <c r="AO24" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="148"/>
         <v>2.1337581740735967E-2</v>
       </c>
       <c r="AP24" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="148"/>
         <v>-4.9759166677544431E-2</v>
       </c>
       <c r="AQ24" s="10">
-        <f t="shared" si="126"/>
-        <v>-2.0000000000000018E-2</v>
+        <f t="shared" si="148"/>
+        <v>-6.5003914996497048E-2</v>
       </c>
       <c r="AR24" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="148"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AS24" s="10">
+        <f t="shared" si="148"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AT24" s="10">
+        <f t="shared" si="148"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS24" s="10">
-        <f t="shared" si="126"/>
+      <c r="AU24" s="10">
+        <f t="shared" si="148"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT24" s="10">
-        <f t="shared" si="126"/>
+      <c r="AV24" s="10">
+        <f t="shared" si="148"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU24" s="10">
-        <f t="shared" si="126"/>
+      <c r="AW24" s="10">
+        <f t="shared" si="148"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AV24" s="10">
-        <f t="shared" si="126"/>
+      <c r="AX24" s="10">
+        <f t="shared" ref="AX24:BA24" si="149">AX3/AW3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AW24" s="10">
-        <f t="shared" si="126"/>
+      <c r="AY24" s="10">
+        <f t="shared" si="149"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AX24" s="10">
-        <f t="shared" ref="AX24:BA24" si="127">AX3/AW3-1</f>
+      <c r="AZ24" s="10">
+        <f t="shared" si="149"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AY24" s="10">
-        <f t="shared" si="127"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AZ24" s="10">
-        <f t="shared" si="127"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="BA24" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="149"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4973,192 +5196,204 @@
         <v>29</v>
       </c>
       <c r="C25" s="10">
-        <f t="shared" ref="C25:Q25" si="128">C5/C3</f>
+        <f t="shared" ref="C25:Q25" si="150">C5/C3</f>
         <v>0.21679024758074653</v>
       </c>
       <c r="D25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.20242418294238884</v>
       </c>
       <c r="E25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.19805525851135261</v>
       </c>
       <c r="F25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.17652864192233425</v>
       </c>
       <c r="G25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.19071489747594336</v>
       </c>
       <c r="H25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.13003516998827666</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.20046221400508435</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.15647081290979692</v>
       </c>
       <c r="K25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.15342664481637697</v>
       </c>
       <c r="L25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>8.9285714285714288E-2</v>
       </c>
       <c r="M25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.18810357240386286</v>
       </c>
       <c r="N25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.20602303682889686</v>
       </c>
       <c r="O25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.22462137339577884</v>
       </c>
       <c r="P25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.23156722541319893</v>
       </c>
       <c r="Q25" s="10">
-        <f t="shared" si="128"/>
+        <f t="shared" si="150"/>
         <v>0.21215281069295669</v>
       </c>
       <c r="R25" s="10">
-        <f t="shared" ref="R25:AD25" si="129">R5/R3</f>
+        <f t="shared" ref="R25:AD25" si="151">R5/R3</f>
         <v>0.24611237230419977</v>
       </c>
       <c r="S25" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="151"/>
         <v>0.22846979172643295</v>
       </c>
       <c r="T25" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="151"/>
         <v>0.23331503841931944</v>
       </c>
       <c r="U25" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="151"/>
         <v>0.23284547672075512</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="151"/>
         <v>0.21393556569031535</v>
       </c>
       <c r="W25" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="151"/>
         <v>0.25189252585563493</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="151"/>
         <v>0.23422504641615022</v>
       </c>
       <c r="Y25" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="151"/>
         <v>0.21596774193548388</v>
       </c>
       <c r="Z25" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="151"/>
         <v>0.19716350810958497</v>
       </c>
       <c r="AA25" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="151"/>
         <v>0.19808769826889305</v>
       </c>
       <c r="AB25" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="151"/>
         <v>0.21293851890155949</v>
       </c>
       <c r="AC25" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="151"/>
         <v>0.17991195551436515</v>
       </c>
       <c r="AD25" s="10">
-        <f t="shared" si="129"/>
+        <f t="shared" si="151"/>
         <v>0.2</v>
       </c>
-      <c r="AE25" s="10"/>
-      <c r="AF25" s="10"/>
-      <c r="AG25" s="10"/>
-      <c r="AH25" s="10"/>
+      <c r="AE25" s="10">
+        <f t="shared" ref="AE25:AH25" si="152">AE5/AE3</f>
+        <v>0.19756802311581989</v>
+      </c>
+      <c r="AF25" s="10">
+        <f t="shared" si="152"/>
+        <v>0.16414804090127591</v>
+      </c>
+      <c r="AG25" s="10">
+        <f t="shared" si="152"/>
+        <v>0.2</v>
+      </c>
+      <c r="AH25" s="10">
+        <f t="shared" si="152"/>
+        <v>0.2</v>
+      </c>
       <c r="AJ25" s="10">
-        <f t="shared" ref="AJ25:AW25" si="130">AJ5/AJ3</f>
+        <f t="shared" ref="AJ25:AW25" si="153">AJ5/AJ3</f>
         <v>0.19757770581135503</v>
       </c>
       <c r="AK25" s="10">
-        <f t="shared" si="130"/>
+        <f t="shared" si="153"/>
         <v>0.16883267243624997</v>
       </c>
       <c r="AL25" s="10">
-        <f t="shared" si="130"/>
+        <f t="shared" si="153"/>
         <v>0.16582312114005016</v>
       </c>
       <c r="AM25" s="10">
-        <f t="shared" si="130"/>
+        <f t="shared" si="153"/>
         <v>0.22910084918554369</v>
       </c>
       <c r="AN25" s="10">
-        <f t="shared" si="130"/>
+        <f t="shared" si="153"/>
         <v>0.22677429891278988</v>
       </c>
       <c r="AO25" s="10">
-        <f t="shared" si="130"/>
+        <f t="shared" si="153"/>
         <v>0.22437964207860694</v>
       </c>
       <c r="AP25" s="10">
-        <f t="shared" si="130"/>
+        <f t="shared" si="153"/>
         <v>0.19627182438836765</v>
       </c>
       <c r="AQ25" s="10">
-        <f t="shared" si="130"/>
+        <f t="shared" si="153"/>
+        <v>0.19067507765748909</v>
+      </c>
+      <c r="AR25" s="10">
+        <f t="shared" si="153"/>
         <v>0.21</v>
       </c>
-      <c r="AR25" s="10">
-        <f t="shared" si="130"/>
+      <c r="AS25" s="10">
+        <f t="shared" si="153"/>
         <v>0.21</v>
       </c>
-      <c r="AS25" s="10">
-        <f t="shared" si="130"/>
-        <v>0.21</v>
-      </c>
       <c r="AT25" s="10">
-        <f t="shared" si="130"/>
-        <v>0.21</v>
+        <f t="shared" si="153"/>
+        <v>0.22</v>
       </c>
       <c r="AU25" s="10">
-        <f t="shared" si="130"/>
-        <v>0.21</v>
+        <f t="shared" si="153"/>
+        <v>0.22</v>
       </c>
       <c r="AV25" s="10">
-        <f t="shared" si="130"/>
-        <v>0.21</v>
+        <f t="shared" si="153"/>
+        <v>0.22</v>
       </c>
       <c r="AW25" s="10">
-        <f t="shared" si="130"/>
-        <v>0.21</v>
+        <f t="shared" si="153"/>
+        <v>0.22</v>
       </c>
       <c r="AX25" s="10">
-        <f t="shared" ref="AX25:BA25" si="131">AX5/AX3</f>
-        <v>0.21</v>
+        <f t="shared" ref="AX25:BA25" si="154">AX5/AX3</f>
+        <v>0.22</v>
       </c>
       <c r="AY25" s="10">
-        <f t="shared" si="131"/>
-        <v>0.21</v>
+        <f t="shared" si="154"/>
+        <v>0.22000000000000003</v>
       </c>
       <c r="AZ25" s="10">
-        <f t="shared" si="131"/>
-        <v>0.20999999999999996</v>
+        <f t="shared" si="154"/>
+        <v>0.22</v>
       </c>
       <c r="BA25" s="10">
-        <f t="shared" si="131"/>
-        <v>0.21</v>
+        <f t="shared" si="154"/>
+        <v>0.21999999999999997</v>
       </c>
     </row>
     <row r="26" spans="2:132" x14ac:dyDescent="0.3">
@@ -5166,192 +5401,204 @@
         <v>30</v>
       </c>
       <c r="C26" s="10">
-        <f t="shared" ref="C26:Q26" si="132">C14/C3</f>
+        <f t="shared" ref="C26:Q26" si="155">C14/C3</f>
         <v>8.3725021993213522E-2</v>
       </c>
       <c r="D26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>6.4677593483168122E-2</v>
       </c>
       <c r="E26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>6.1799010221083785E-2</v>
       </c>
       <c r="F26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>5.7176571551169279E-2</v>
       </c>
       <c r="G26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>7.0482140158194373E-2</v>
       </c>
       <c r="H26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>-3.6529894490035172E-2</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>6.2167783683845623E-2</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>8.1269760434570411E-3</v>
       </c>
       <c r="K26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>1.6575773043548344E-2</v>
       </c>
       <c r="L26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>-5.5724887357540422E-2</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>7.6214592487773389E-2</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>9.8625083117050261E-2</v>
       </c>
       <c r="O26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>0.14296575634085518</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>0.12817958035400304</v>
       </c>
       <c r="Q26" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="155"/>
         <v>8.9676746611053182E-2</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" ref="R26:AD26" si="133">R14/R3</f>
+        <f t="shared" ref="R26:AD26" si="156">R14/R3</f>
         <v>0.11677071509648126</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" si="133"/>
+        <f t="shared" si="156"/>
         <v>0.15000860634574559</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" si="133"/>
+        <f t="shared" si="156"/>
         <v>0.12683863885839736</v>
       </c>
       <c r="U26" s="10">
-        <f t="shared" si="133"/>
+        <f t="shared" si="156"/>
         <v>0.13776646516067451</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="133"/>
+        <f t="shared" si="156"/>
         <v>0.1319659537107041</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="133"/>
+        <f t="shared" si="156"/>
         <v>0.14671073675231902</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" si="133"/>
+        <f t="shared" si="156"/>
         <v>0.13043591956277295</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="133"/>
+        <f t="shared" si="156"/>
         <v>0.13016129032258064</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" si="133"/>
+        <f t="shared" si="156"/>
         <v>0.10744889595390079</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" si="133"/>
+        <f t="shared" si="156"/>
         <v>0.10768544587851588</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="133"/>
+        <f t="shared" si="156"/>
         <v>0.10987126799662521</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" si="133"/>
+        <f t="shared" si="156"/>
         <v>7.2897358665430956E-2</v>
       </c>
       <c r="AD26" s="10">
-        <f t="shared" si="133"/>
+        <f t="shared" si="156"/>
         <v>8.9414824447334201E-2</v>
       </c>
-      <c r="AE26" s="10"/>
-      <c r="AF26" s="10"/>
-      <c r="AG26" s="10"/>
-      <c r="AH26" s="10"/>
+      <c r="AE26" s="10">
+        <f t="shared" ref="AE26:AH26" si="157">AE14/AE3</f>
+        <v>6.8895978810498429E-2</v>
+      </c>
+      <c r="AF26" s="10">
+        <f t="shared" si="157"/>
+        <v>3.8397731728652004E-2</v>
+      </c>
+      <c r="AG26" s="10">
+        <f t="shared" si="157"/>
+        <v>8.273462918778221E-2</v>
+      </c>
+      <c r="AH26" s="10">
+        <f t="shared" si="157"/>
+        <v>8.4784765326505196E-2</v>
+      </c>
       <c r="AJ26" s="10">
-        <f t="shared" ref="AJ26:AW26" si="134">AJ14/AJ3</f>
+        <f t="shared" ref="AJ26:AW26" si="158">AJ14/AJ3</f>
         <v>6.6424875419748813E-2</v>
       </c>
       <c r="AK26" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="158"/>
         <v>2.4967437552461721E-2</v>
       </c>
       <c r="AL26" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="158"/>
         <v>4.2790763986546472E-2</v>
       </c>
       <c r="AM26" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="158"/>
         <v>0.11970752765267788</v>
       </c>
       <c r="AN26" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="158"/>
         <v>0.13637121126272356</v>
       </c>
       <c r="AO26" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="158"/>
         <v>0.1283139056768787</v>
       </c>
       <c r="AP26" s="10">
-        <f t="shared" si="134"/>
+        <f t="shared" si="158"/>
         <v>9.3403574323117716E-2</v>
       </c>
       <c r="AQ26" s="10">
-        <f t="shared" si="134"/>
-        <v>0.10801491735614804</v>
+        <f t="shared" si="158"/>
+        <v>6.9121053711817232E-2</v>
       </c>
       <c r="AR26" s="10">
-        <f t="shared" si="134"/>
-        <v>0.10684450281701184</v>
+        <f t="shared" si="158"/>
+        <v>9.4667663251537609E-2</v>
       </c>
       <c r="AS26" s="10">
-        <f t="shared" si="134"/>
-        <v>0.10624770728468004</v>
+        <f t="shared" si="158"/>
+        <v>9.4531997765326253E-2</v>
       </c>
       <c r="AT26" s="10">
-        <f t="shared" si="134"/>
-        <v>0.10564500288569149</v>
+        <f t="shared" si="158"/>
+        <v>0.10389664908867262</v>
       </c>
       <c r="AU26" s="10">
-        <f t="shared" si="134"/>
-        <v>0.10503633111641589</v>
+        <f t="shared" si="158"/>
+        <v>0.10325500983106199</v>
       </c>
       <c r="AV26" s="10">
-        <f t="shared" si="134"/>
-        <v>0.10484462168189347</v>
+        <f t="shared" si="158"/>
+        <v>0.10307085814144865</v>
       </c>
       <c r="AW26" s="10">
-        <f t="shared" si="134"/>
-        <v>0.10465101413415795</v>
+        <f t="shared" si="158"/>
+        <v>0.10307085814144863</v>
       </c>
       <c r="AX26" s="10">
-        <f t="shared" ref="AX26:BA26" si="135">AX14/AX3</f>
-        <v>0.10445548968000919</v>
+        <f t="shared" ref="AX26:BA26" si="159">AX14/AX3</f>
+        <v>0.10307085814144867</v>
       </c>
       <c r="AY26" s="10">
-        <f t="shared" si="135"/>
-        <v>0.10425802934017578</v>
+        <f t="shared" si="159"/>
+        <v>0.10307085814144869</v>
       </c>
       <c r="AZ26" s="10">
-        <f t="shared" si="135"/>
-        <v>0.10405861394747275</v>
+        <f t="shared" si="159"/>
+        <v>0.10307085814144865</v>
       </c>
       <c r="BA26" s="10">
-        <f t="shared" si="135"/>
-        <v>0.10385722414494097</v>
+        <f t="shared" si="159"/>
+        <v>0.10307085814144865</v>
       </c>
       <c r="BC26" s="1" t="s">
         <v>32</v>
@@ -5369,194 +5616,206 @@
         <v>7.7843408319718491E-2</v>
       </c>
       <c r="D27" s="11">
-        <f t="shared" ref="D27:Q27" si="136">D6/D3</f>
+        <f t="shared" ref="D27:Q27" si="160">D6/D3</f>
         <v>7.9816468740798896E-2</v>
       </c>
       <c r="E27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>7.9356395016289077E-2</v>
       </c>
       <c r="F27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>7.5649002360008585E-2</v>
       </c>
       <c r="G27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>7.9374275782155279E-2</v>
       </c>
       <c r="H27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>7.2028135990621342E-2</v>
       </c>
       <c r="I27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>7.2475155997226717E-2</v>
       </c>
       <c r="J27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>7.303668809811785E-2</v>
       </c>
       <c r="K27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>7.7613303602611289E-2</v>
       </c>
       <c r="L27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>8.1566392790882583E-2</v>
       </c>
       <c r="M27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>5.8687718775601402E-2</v>
       </c>
       <c r="N27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>7.1705883614680083E-2</v>
       </c>
       <c r="O27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>6.7362082598382098E-2</v>
       </c>
       <c r="P27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>6.5789473684210523E-2</v>
       </c>
       <c r="Q27" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="160"/>
         <v>6.9485259266281157E-2</v>
       </c>
       <c r="R27" s="11">
-        <f t="shared" ref="R27:AD27" si="137">R6/R3</f>
+        <f t="shared" ref="R27:AD27" si="161">R6/R3</f>
         <v>7.193530079455164E-2</v>
       </c>
       <c r="S27" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="161"/>
         <v>6.383039761317344E-2</v>
       </c>
       <c r="T27" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="161"/>
         <v>6.6026344676180015E-2</v>
       </c>
       <c r="U27" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="161"/>
         <v>6.5118252200657548E-2</v>
       </c>
       <c r="V27" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="161"/>
         <v>5.841036021754506E-2</v>
       </c>
       <c r="W27" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="161"/>
         <v>6.2746561467107373E-2</v>
       </c>
       <c r="X27" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="161"/>
         <v>6.5950158207159854E-2</v>
       </c>
       <c r="Y27" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="161"/>
         <v>6.3655913978494627E-2</v>
       </c>
       <c r="Z27" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="161"/>
         <v>6.1697424306400732E-2</v>
       </c>
       <c r="AA27" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="161"/>
         <v>6.536949795110529E-2</v>
       </c>
       <c r="AB27" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="161"/>
         <v>6.6434422883270283E-2</v>
       </c>
       <c r="AC27" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="161"/>
         <v>6.2065569972196477E-2</v>
       </c>
       <c r="AD27" s="11">
-        <f t="shared" si="137"/>
+        <f t="shared" si="161"/>
         <v>7.9687906371911574E-2</v>
       </c>
-      <c r="AE27" s="11"/>
-      <c r="AF27" s="11"/>
-      <c r="AG27" s="11"/>
-      <c r="AH27" s="11"/>
+      <c r="AE27" s="11">
+        <f t="shared" ref="AE27:AH27" si="162">AE6/AE3</f>
+        <v>7.2236937153864672E-2</v>
+      </c>
+      <c r="AF27" s="11">
+        <f t="shared" si="162"/>
+        <v>7.3899797906675113E-2</v>
+      </c>
+      <c r="AG27" s="11">
+        <f t="shared" si="162"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AH27" s="11">
+        <f t="shared" si="162"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="AJ27" s="11">
-        <f t="shared" ref="AJ27:AW27" si="138">AJ6/AJ3</f>
+        <f t="shared" ref="AJ27:AW27" si="163">AJ6/AJ3</f>
         <v>7.8076265819003121E-2</v>
       </c>
       <c r="AK27" s="11">
-        <f t="shared" si="138"/>
+        <f t="shared" si="163"/>
         <v>7.4103447277779386E-2</v>
       </c>
       <c r="AL27" s="11">
-        <f t="shared" si="138"/>
+        <f t="shared" si="163"/>
         <v>7.1661406658069193E-2</v>
       </c>
       <c r="AM27" s="11">
-        <f t="shared" si="138"/>
+        <f t="shared" si="163"/>
         <v>6.8666771227771428E-2</v>
       </c>
       <c r="AN27" s="11">
-        <f t="shared" si="138"/>
+        <f t="shared" si="163"/>
         <v>6.3206169967403691E-2</v>
       </c>
       <c r="AO27" s="11">
-        <f t="shared" si="138"/>
+        <f t="shared" si="163"/>
         <v>6.3491234711326339E-2</v>
       </c>
       <c r="AP27" s="11">
-        <f t="shared" si="138"/>
+        <f t="shared" si="163"/>
         <v>6.8636070167726687E-2</v>
       </c>
       <c r="AQ27" s="11">
-        <f t="shared" si="138"/>
+        <f t="shared" si="163"/>
+        <v>7.1495704614903635E-2</v>
+      </c>
+      <c r="AR27" s="11">
+        <f t="shared" si="163"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AR27" s="11">
-        <f t="shared" si="138"/>
+      <c r="AS27" s="11">
+        <f t="shared" si="163"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AS27" s="11">
-        <f t="shared" si="138"/>
+      <c r="AT27" s="11">
+        <f t="shared" si="163"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AT27" s="11">
-        <f t="shared" si="138"/>
+      <c r="AU27" s="11">
+        <f t="shared" si="163"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AU27" s="11">
-        <f t="shared" si="138"/>
+      <c r="AV27" s="11">
+        <f t="shared" si="163"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AV27" s="11">
-        <f t="shared" si="138"/>
+      <c r="AW27" s="11">
+        <f t="shared" si="163"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AW27" s="11">
-        <f t="shared" si="138"/>
+      <c r="AX27" s="11">
+        <f t="shared" ref="AX27:BA27" si="164">AX6/AX3</f>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AX27" s="11">
-        <f t="shared" ref="AX27:BA27" si="139">AX6/AX3</f>
+      <c r="AY27" s="11">
+        <f t="shared" si="164"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AY27" s="11">
-        <f t="shared" si="139"/>
+      <c r="AZ27" s="11">
+        <f t="shared" si="164"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AZ27" s="11">
-        <f t="shared" si="139"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
       <c r="BA27" s="11">
-        <f t="shared" si="139"/>
+        <f t="shared" si="164"/>
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="BC27" s="1" t="s">
         <v>33</v>
       </c>
       <c r="BD27" s="11">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="28" spans="2:132" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -5568,35 +5827,35 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="11">
-        <f t="shared" ref="G28:N29" si="140">G7/C7-1</f>
+        <f t="shared" ref="G28:N29" si="165">G7/C7-1</f>
         <v>4.9433573635427441E-2</v>
       </c>
       <c r="H28" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>1.0362694300518172E-2</v>
       </c>
       <c r="I28" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>5.4564533053515163E-2</v>
       </c>
       <c r="J28" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>-8.3696599825632045E-2</v>
       </c>
       <c r="K28" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>-9.7154072620215914E-2</v>
       </c>
       <c r="L28" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>-0.17128205128205132</v>
       </c>
       <c r="M28" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>-0.11641791044776117</v>
       </c>
       <c r="N28" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>-0.12654614652711704</v>
       </c>
       <c r="O28" s="11"/>
@@ -5604,57 +5863,69 @@
       <c r="Q28" s="11"/>
       <c r="R28" s="11"/>
       <c r="S28" s="11">
-        <f t="shared" ref="S28:AD28" si="141">S7/O7-1</f>
+        <f t="shared" ref="S28:AE28" si="166">S7/O7-1</f>
         <v>-0.10162002945508097</v>
       </c>
       <c r="T28" s="11">
-        <f t="shared" si="141"/>
+        <f t="shared" si="166"/>
         <v>-9.3701996927803344E-2</v>
       </c>
       <c r="U28" s="11">
-        <f t="shared" si="141"/>
+        <f t="shared" si="166"/>
         <v>-0.13154172560113153</v>
       </c>
       <c r="V28" s="11">
-        <f t="shared" si="141"/>
+        <f t="shared" si="166"/>
         <v>-1.2970168612191912E-3</v>
       </c>
       <c r="W28" s="11">
-        <f t="shared" si="141"/>
+        <f t="shared" si="166"/>
         <v>0.16721311475409828</v>
       </c>
       <c r="X28" s="11">
-        <f t="shared" si="141"/>
+        <f t="shared" si="166"/>
         <v>0.18813559322033901</v>
       </c>
       <c r="Y28" s="11">
-        <f t="shared" si="141"/>
+        <f t="shared" si="166"/>
         <v>-1.3029315960912058E-2</v>
       </c>
       <c r="Z28" s="11">
-        <f t="shared" si="141"/>
+        <f t="shared" si="166"/>
         <v>-0.13116883116883116</v>
       </c>
       <c r="AA28" s="11">
-        <f t="shared" si="141"/>
+        <f t="shared" si="166"/>
         <v>5.6179775280897903E-3</v>
       </c>
       <c r="AB28" s="11">
-        <f t="shared" si="141"/>
+        <f t="shared" si="166"/>
         <v>-0.11697574893009988</v>
       </c>
       <c r="AC28" s="11">
-        <f t="shared" si="141"/>
+        <f t="shared" si="166"/>
         <v>6.6006600660066805E-3</v>
       </c>
       <c r="AD28" s="11">
-        <f t="shared" si="141"/>
+        <f t="shared" si="166"/>
         <v>-0.12705530642750373</v>
       </c>
-      <c r="AE28" s="11"/>
-      <c r="AF28" s="11"/>
-      <c r="AG28" s="11"/>
-      <c r="AH28" s="11"/>
+      <c r="AE28" s="11">
+        <f t="shared" si="166"/>
+        <v>-7.8212290502793325E-2</v>
+      </c>
+      <c r="AF28" s="11">
+        <f t="shared" ref="AF28:AF29" si="167">AF7/AB7-1</f>
+        <v>8.5621970920840118E-2</v>
+      </c>
+      <c r="AG28" s="11">
+        <f t="shared" ref="AG28:AG29" si="168">AG7/AC7-1</f>
+        <v>-9.9999999999999978E-2</v>
+      </c>
+      <c r="AH28" s="11">
+        <f t="shared" ref="AH28:AH29" si="169">AH7/AD7-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
       <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
       <c r="AK28" s="11">
@@ -5667,67 +5938,67 @@
       </c>
       <c r="AM28" s="11"/>
       <c r="AN28" s="11">
-        <f t="shared" ref="AN28:AW28" si="142">AN7/AM7-1</f>
+        <f t="shared" ref="AN28:AW28" si="170">AN7/AM7-1</f>
         <v>-7.9772079772079785E-2</v>
       </c>
       <c r="AO28" s="11">
-        <f t="shared" si="142"/>
+        <f t="shared" si="170"/>
         <v>4.0247678018575872E-2</v>
       </c>
       <c r="AP28" s="11">
-        <f t="shared" si="142"/>
+        <f t="shared" si="170"/>
         <v>-5.9151785714285698E-2</v>
       </c>
       <c r="AQ28" s="11">
-        <f t="shared" si="142"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="170"/>
+        <v>-1.8378805852115487E-2</v>
       </c>
       <c r="AR28" s="11">
-        <f t="shared" si="142"/>
+        <f t="shared" si="170"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AS28" s="11">
-        <f t="shared" si="142"/>
+        <f t="shared" si="170"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT28" s="11">
-        <f t="shared" si="142"/>
+        <f t="shared" si="170"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU28" s="11">
-        <f t="shared" si="142"/>
+        <f t="shared" si="170"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AV28" s="11">
-        <f t="shared" si="142"/>
+        <f t="shared" si="170"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW28" s="11">
-        <f t="shared" si="142"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="170"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX28" s="11">
-        <f t="shared" ref="AX28:BA28" si="143">AX7/AW7-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AX28:BA28" si="171">AX7/AW7-1</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY28" s="11">
-        <f t="shared" si="143"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="171"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ28" s="11">
-        <f t="shared" si="143"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="171"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA28" s="11">
-        <f t="shared" si="143"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="171"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC28" s="1" t="s">
         <v>34</v>
       </c>
       <c r="BD28" s="6">
         <f>NPV(BD27,AQ20:EB20)</f>
-        <v>138082.99757655308</v>
+        <v>145461.79581528198</v>
       </c>
     </row>
     <row r="29" spans="2:132" x14ac:dyDescent="0.3">
@@ -5735,35 +6006,35 @@
         <v>51</v>
       </c>
       <c r="G29" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>-4.6728971962616273E-3</v>
       </c>
       <c r="H29" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>-3.1481481481481444E-2</v>
       </c>
       <c r="I29" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>-6.1971830985915188E-3</v>
       </c>
       <c r="J29" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>5.0881953867028429E-2</v>
       </c>
       <c r="K29" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>1.0563380281690238E-2</v>
       </c>
       <c r="L29" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>-1.5933715742511123E-2</v>
       </c>
       <c r="M29" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>-0.11904761904761907</v>
       </c>
       <c r="N29" s="11">
-        <f t="shared" si="140"/>
+        <f t="shared" si="165"/>
         <v>-0.16333118140735958</v>
       </c>
       <c r="O29" s="11"/>
@@ -5771,57 +6042,69 @@
       <c r="Q29" s="11"/>
       <c r="R29" s="11"/>
       <c r="S29" s="11">
-        <f t="shared" ref="S29:AD29" si="144">S8/O8-1</f>
+        <f t="shared" ref="S29:AE29" si="172">S8/O8-1</f>
         <v>-9.1688654353561994E-2</v>
       </c>
       <c r="T29" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="172"/>
         <v>-2.3584905660377409E-2</v>
       </c>
       <c r="U29" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="172"/>
         <v>0.12879348630643972</v>
       </c>
       <c r="V29" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="172"/>
         <v>0.12096774193548376</v>
       </c>
       <c r="W29" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="172"/>
         <v>0.22222222222222232</v>
       </c>
       <c r="X29" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="172"/>
         <v>0.13457556935817805</v>
       </c>
       <c r="Y29" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="172"/>
         <v>1.0491803278688483E-2</v>
       </c>
       <c r="Z29" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="172"/>
         <v>8.8729016786570636E-2</v>
       </c>
       <c r="AA29" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="172"/>
         <v>-0.12774806892453949</v>
       </c>
       <c r="AB29" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="172"/>
         <v>-0.11131386861313863</v>
       </c>
       <c r="AC29" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="172"/>
         <v>9.1499026606099987E-2</v>
       </c>
       <c r="AD29" s="11">
-        <f t="shared" si="144"/>
+        <f t="shared" si="172"/>
         <v>-0.28854625550660795</v>
       </c>
-      <c r="AE29" s="11"/>
-      <c r="AF29" s="11"/>
-      <c r="AG29" s="11"/>
-      <c r="AH29" s="11"/>
+      <c r="AE29" s="11">
+        <f t="shared" si="172"/>
+        <v>9.4686648501362436E-2</v>
+      </c>
+      <c r="AF29" s="11">
+        <f t="shared" si="167"/>
+        <v>-6.8446269678301697E-4</v>
+      </c>
+      <c r="AG29" s="11">
+        <f t="shared" si="168"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AH29" s="11">
+        <f t="shared" si="169"/>
+        <v>0.5</v>
+      </c>
       <c r="AK29" s="11">
         <f>AK8/AJ8-1</f>
         <v>7.5976295395840943E-4</v>
@@ -5832,59 +6115,59 @@
       </c>
       <c r="AM29" s="11"/>
       <c r="AN29" s="11">
-        <f t="shared" ref="AN29:AW29" si="145">AN8/AM8-1</f>
+        <f t="shared" ref="AN29:AW29" si="173">AN8/AM8-1</f>
         <v>2.4693616242912109E-2</v>
       </c>
       <c r="AO29" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="173"/>
         <v>0.11210282042127817</v>
       </c>
       <c r="AP29" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="173"/>
         <v>-0.1043338683788122</v>
       </c>
       <c r="AQ29" s="11">
-        <f t="shared" si="145"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="173"/>
+        <v>0.12060215053763446</v>
       </c>
       <c r="AR29" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="173"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AS29" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="173"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT29" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="173"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU29" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="173"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AV29" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="173"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW29" s="11">
-        <f t="shared" si="145"/>
+        <f t="shared" si="173"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX29" s="11">
-        <f t="shared" ref="AX29:BA29" si="146">AX8/AW8-1</f>
+        <f t="shared" ref="AX29:BA29" si="174">AX8/AW8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY29" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="174"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ29" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="174"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA29" s="11">
-        <f t="shared" si="146"/>
+        <f t="shared" si="174"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC29" s="1" t="s">
@@ -5892,7 +6175,7 @@
       </c>
       <c r="BD29" s="6">
         <f>Main!D8</f>
-        <v>-91201</v>
+        <v>-83984</v>
       </c>
     </row>
     <row r="30" spans="2:132" x14ac:dyDescent="0.3">
@@ -5900,191 +6183,203 @@
         <v>25</v>
       </c>
       <c r="C30" s="10">
-        <f t="shared" ref="C30:N30" si="147">C18/C17</f>
+        <f t="shared" ref="C30:N30" si="175">C18/C17</f>
         <v>0.27502309824453341</v>
       </c>
       <c r="D30" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="175"/>
         <v>0.27865612648221344</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="175"/>
         <v>0.24904051172707889</v>
       </c>
       <c r="F30" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="175"/>
         <v>0.33602911443590783</v>
       </c>
       <c r="G30" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="175"/>
         <v>0.18070911170415555</v>
       </c>
       <c r="H30" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="175"/>
         <v>0.25717703349282295</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="175"/>
         <v>0.2959223300970874</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="175"/>
         <v>1.0361842105263157</v>
       </c>
       <c r="K30" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="175"/>
         <v>0.68888888888888888</v>
       </c>
       <c r="L30" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="175"/>
         <v>-9.4144661308840416E-2</v>
       </c>
       <c r="M30" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="175"/>
         <v>0.28825857519788917</v>
       </c>
       <c r="N30" s="10">
-        <f t="shared" si="147"/>
+        <f t="shared" si="175"/>
         <v>0.20403637170104236</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" ref="O30:Q30" si="148">O18/O17</f>
+        <f t="shared" ref="O30:Q30" si="176">O18/O17</f>
         <v>0.25504508372692142</v>
       </c>
       <c r="P30" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="176"/>
         <v>0.27067843866171004</v>
       </c>
       <c r="Q30" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="176"/>
         <v>0.30329904221355092</v>
       </c>
       <c r="R30" s="10">
-        <f t="shared" ref="R30:AD30" si="149">R18/R17</f>
+        <f t="shared" ref="R30:AD30" si="177">R18/R17</f>
         <v>0.38535980148883375</v>
       </c>
       <c r="S30" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="177"/>
         <v>0.30865625602467706</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="177"/>
         <v>0.2969883490877116</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="177"/>
         <v>0.22609368950832365</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="177"/>
         <v>0.25453535727508331</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="177"/>
         <v>0.27976297360387864</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="177"/>
         <v>0.28397246804326448</v>
       </c>
       <c r="Y30" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="177"/>
         <v>0.2532128514056225</v>
       </c>
       <c r="Z30" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="177"/>
         <v>0.28988764044943821</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="177"/>
         <v>0.2491933482253661</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="177"/>
         <v>0.26500240038406148</v>
       </c>
       <c r="AC30" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="177"/>
         <v>0.35009451795841212</v>
       </c>
       <c r="AD30" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="177"/>
         <v>0.19758630367667696</v>
       </c>
-      <c r="AE30" s="10"/>
-      <c r="AF30" s="10"/>
-      <c r="AG30" s="10"/>
-      <c r="AH30" s="10"/>
+      <c r="AE30" s="10">
+        <f t="shared" ref="AE30:AH30" si="178">AE18/AE17</f>
+        <v>0.2853014037985136</v>
+      </c>
+      <c r="AF30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.31740370898716119</v>
+      </c>
+      <c r="AG30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AH30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.28000000000000003</v>
+      </c>
       <c r="AJ30" s="10">
-        <f t="shared" ref="AJ30:AW30" si="150">AJ18/AJ17</f>
+        <f t="shared" ref="AJ30:AW30" si="179">AJ18/AJ17</f>
         <v>0.28437942425672486</v>
       </c>
       <c r="AK30" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="179"/>
         <v>0.29268929503916447</v>
       </c>
       <c r="AL30" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="179"/>
         <v>0.36756586212336329</v>
       </c>
       <c r="AM30" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="179"/>
         <v>0.30111947378407439</v>
       </c>
       <c r="AN30" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="179"/>
         <v>0.27063632781717889</v>
       </c>
       <c r="AO30" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="179"/>
         <v>0.27648874726150169</v>
       </c>
       <c r="AP30" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="179"/>
         <v>0.26422563087580409</v>
       </c>
       <c r="AQ30" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="179"/>
+        <v>0.28657602696074319</v>
+      </c>
+      <c r="AR30" s="10">
+        <f t="shared" si="179"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="AR30" s="10">
-        <f t="shared" si="150"/>
+      <c r="AS30" s="10">
+        <f t="shared" si="179"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="AS30" s="10">
-        <f t="shared" si="150"/>
-        <v>0.28000000000000008</v>
-      </c>
       <c r="AT30" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="179"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="AU30" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="179"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="AV30" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="179"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="AW30" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="179"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="AX30" s="10">
-        <f t="shared" ref="AX30:BA30" si="151">AX18/AX17</f>
+        <f t="shared" ref="AX30:BA30" si="180">AX18/AX17</f>
         <v>0.28000000000000003</v>
       </c>
       <c r="AY30" s="10">
-        <f t="shared" si="151"/>
+        <f t="shared" si="180"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="AZ30" s="10">
-        <f t="shared" si="151"/>
+        <f t="shared" si="180"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="BA30" s="10">
-        <f t="shared" si="151"/>
+        <f t="shared" si="180"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="BC30" s="1" t="s">
@@ -6092,7 +6387,7 @@
       </c>
       <c r="BD30" s="6">
         <f>BD28+BD29</f>
-        <v>46881.997576553083</v>
+        <v>61477.795815281977</v>
       </c>
     </row>
     <row r="31" spans="2:132" x14ac:dyDescent="0.3">
@@ -6100,199 +6395,211 @@
         <v>52</v>
       </c>
       <c r="C31" s="10">
-        <f t="shared" ref="C31:Q31" si="152">C20/C3</f>
+        <f t="shared" ref="C31:Q31" si="181">C20/C3</f>
         <v>5.7132084956641953E-2</v>
       </c>
       <c r="D31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>4.2349592698007657E-2</v>
       </c>
       <c r="E31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>4.2003431896744672E-2</v>
       </c>
       <c r="F31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>3.3490667238789962E-2</v>
       </c>
       <c r="G31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>5.2773439467983276E-2</v>
       </c>
       <c r="H31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>-3.1137162954279016E-2</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>3.9727293737000229E-2</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>-2.3128991873023956E-3</v>
       </c>
       <c r="K31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>2.5253203664401041E-3</v>
       </c>
       <c r="L31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>-6.6293400477073952E-2</v>
       </c>
       <c r="M31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>5.0867654725552991E-2</v>
       </c>
       <c r="N31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>7.4751721327298862E-2</v>
       </c>
       <c r="O31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>0.10300468341341767</v>
       </c>
       <c r="P31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>8.8881725471808698E-2</v>
       </c>
       <c r="Q31" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="181"/>
         <v>5.8804942016620849E-2</v>
       </c>
       <c r="R31" s="10">
-        <f t="shared" ref="R31:AD31" si="153">R20/R3</f>
+        <f t="shared" ref="R31:AD31" si="182">R20/R3</f>
         <v>6.7508513053348471E-2</v>
       </c>
       <c r="S31" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="182"/>
         <v>0.10012048884043835</v>
       </c>
       <c r="T31" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="182"/>
         <v>8.5263446761800213E-2</v>
       </c>
       <c r="U31" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="182"/>
         <v>0.10401421147523597</v>
       </c>
       <c r="V31" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="182"/>
         <v>9.7090456795844202E-2</v>
       </c>
       <c r="W31" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="182"/>
         <v>0.10515513380957459</v>
       </c>
       <c r="X31" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="182"/>
         <v>9.3172249679663185E-2</v>
       </c>
       <c r="Y31" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="182"/>
         <v>9.7741935483870973E-2</v>
       </c>
       <c r="Z31" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="182"/>
         <v>7.7419835572886911E-2</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="182"/>
         <v>8.2903576506007298E-2</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="182"/>
         <v>8.2083662194159426E-2</v>
       </c>
       <c r="AC31" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="182"/>
         <v>5.0191149212233548E-2</v>
       </c>
       <c r="AD31" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="182"/>
         <v>7.1261378413524062E-2</v>
       </c>
-      <c r="AE31" s="10"/>
-      <c r="AF31" s="10"/>
-      <c r="AG31" s="10"/>
-      <c r="AH31" s="10"/>
+      <c r="AE31" s="10">
+        <f t="shared" ref="AE31:AH31" si="183">AE20/AE3</f>
+        <v>5.0505658560077056E-2</v>
+      </c>
+      <c r="AF31" s="10">
+        <f t="shared" si="183"/>
+        <v>2.7599312279431725E-2</v>
+      </c>
+      <c r="AG31" s="10">
+        <f t="shared" si="183"/>
+        <v>6.0702480133299139E-2</v>
+      </c>
+      <c r="AH31" s="10">
+        <f t="shared" si="183"/>
+        <v>6.1718861019130496E-2</v>
+      </c>
       <c r="AJ31" s="10">
-        <f t="shared" ref="AJ31:AW31" si="154">AJ20/AJ3</f>
+        <f t="shared" ref="AJ31:AW31" si="184">AJ20/AJ3</f>
         <v>4.3313296925227951E-2</v>
       </c>
       <c r="AK31" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="184"/>
         <v>1.3760166719731397E-2</v>
       </c>
       <c r="AL31" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="184"/>
         <v>2.3504785851764964E-2</v>
       </c>
       <c r="AM31" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="184"/>
         <v>7.9615812626500262E-2</v>
       </c>
       <c r="AN31" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="184"/>
         <v>9.6662378263796769E-2</v>
       </c>
       <c r="AO31" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="184"/>
         <v>9.3076531478024777E-2</v>
       </c>
       <c r="AP31" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="184"/>
         <v>7.0105910957869139E-2</v>
       </c>
       <c r="AQ31" s="10">
-        <f t="shared" si="154"/>
-        <v>7.9095245627132521E-2</v>
+        <f t="shared" si="184"/>
+        <v>5.0430365808167607E-2</v>
       </c>
       <c r="AR31" s="10">
-        <f t="shared" si="154"/>
-        <v>7.8211729372417285E-2</v>
+        <f t="shared" si="184"/>
+        <v>6.9236944170081929E-2</v>
       </c>
       <c r="AS31" s="10">
-        <f t="shared" si="154"/>
-        <v>7.7738872373139367E-2</v>
+        <f t="shared" si="184"/>
+        <v>6.9082382882168031E-2</v>
       </c>
       <c r="AT31" s="10">
-        <f t="shared" si="154"/>
-        <v>7.7259318239916566E-2</v>
+        <f t="shared" si="184"/>
+        <v>7.5776069149667044E-2</v>
       </c>
       <c r="AU31" s="10">
-        <f t="shared" si="154"/>
-        <v>7.677292475730231E-2</v>
+        <f t="shared" si="184"/>
+        <v>7.5262590799292831E-2</v>
       </c>
       <c r="AV31" s="10">
-        <f t="shared" si="154"/>
-        <v>7.6584097300273088E-2</v>
+        <f t="shared" si="184"/>
+        <v>7.5075760421618218E-2</v>
       </c>
       <c r="AW31" s="10">
-        <f t="shared" si="154"/>
-        <v>7.6391148260551919E-2</v>
+        <f t="shared" si="184"/>
+        <v>7.5018664282248099E-2</v>
       </c>
       <c r="AX31" s="10">
-        <f t="shared" ref="AX31:BA31" si="155">AX20/AX3</f>
-        <v>7.6193951788915221E-2</v>
+        <f t="shared" ref="AX31:BA31" si="185">AX20/AX3</f>
+        <v>7.4958596871890215E-2</v>
       </c>
       <c r="AY31" s="10">
-        <f t="shared" si="155"/>
-        <v>7.5992377504243286E-2</v>
+        <f t="shared" si="185"/>
+        <v>7.4895437334924833E-2</v>
       </c>
       <c r="AZ31" s="10">
-        <f t="shared" si="155"/>
-        <v>7.5786290320142571E-2</v>
+        <f t="shared" si="185"/>
+        <v>7.4829060074079773E-2</v>
       </c>
       <c r="BA31" s="10">
-        <f t="shared" si="155"/>
-        <v>7.5575550264794691E-2</v>
+        <f t="shared" si="185"/>
+        <v>7.4759334564594201E-2</v>
       </c>
       <c r="BC31" s="1" t="s">
         <v>37</v>
       </c>
       <c r="BD31" s="4">
         <f>BD30/AV21</f>
-        <v>46.252957356504616</v>
+        <v>60.652916155566274</v>
       </c>
     </row>
     <row r="32" spans="2:132" x14ac:dyDescent="0.3">
@@ -6301,7 +6608,7 @@
       </c>
       <c r="BD32" s="4">
         <f>Main!D3</f>
-        <v>53.31</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="33" spans="55:56" x14ac:dyDescent="0.3">
@@ -6310,7 +6617,7 @@
       </c>
       <c r="BD33" s="10">
         <f>BD31/BD32-1</f>
-        <v>-0.13237746470634748</v>
+        <v>0.1368869007603799</v>
       </c>
     </row>
     <row r="34" spans="55:56" x14ac:dyDescent="0.3">
